--- a/requirements/procurement-ai-chat/Trade Marketing Materials price for Y2026.final.xlsx
+++ b/requirements/procurement-ai-chat/Trade Marketing Materials price for Y2026.final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haadthipo365-my.sharepoint.com/personal/densri_ka_haadthip_com/Documents/densri.ka/Requirement Chatbot by Procurement 15.7.2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/supakorn.emch/Workspace/Haadthip/EnterpriseChat/requirements/procurement-ai-chat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DA3ADC6-D06C-4FE2-B9B9-1E3D62D4EE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D49DD-DD78-4241-8E9A-9E91CDBBFBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.POSM(MKT)" sheetId="27" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'5.Printing-Rate1-43'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'5.Printing-Rate44-109'!$5:$5</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -76,7 +76,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -85,12 +85,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-ทรงกลม</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ทรงกลม</t>
         </r>
       </text>
     </comment>
@@ -100,7 +109,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -109,13 +118,58 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-58 มียางกันลื่น
-55 ไม่มียางกันลื่น</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">58 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>มียางกันลื่น</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">55 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ไม่มียางกันลื่น</t>
         </r>
       </text>
     </comment>
@@ -125,7 +179,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -134,12 +188,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-R 3</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>R 3</t>
         </r>
       </text>
     </comment>
@@ -1733,7 +1796,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1921,6 +1984,19 @@
       <b/>
       <sz val="48"/>
       <name val="Kanit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2974,93 +3050,6 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3115,24 +3104,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3160,34 +3131,55 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="20" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3196,26 +3188,110 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3277,9 +3353,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Old Version"/>
       <sheetName val="Example"/>
@@ -3563,68 +3636,68 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="7"/>
-    <col min="2" max="2" width="12.85546875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="7"/>
+    <col min="2" max="2" width="12.83203125" style="14" customWidth="1"/>
     <col min="3" max="3" width="50" style="10" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="7" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="7" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="7" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="7" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="10.5703125" style="7" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="7" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="7" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="7" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" style="7" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5" style="7" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11" style="9" customWidth="1"/>
     <col min="25" max="25" width="20" style="12" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="18" style="9" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="82.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.7109375" style="7"/>
+    <col min="27" max="27" width="82.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="24" customFormat="1" ht="76.5" customHeight="1">
-      <c r="B1" s="333" t="s">
+      <c r="B1" s="304" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="333"/>
-      <c r="D1" s="333"/>
-      <c r="E1" s="333"/>
-      <c r="F1" s="333"/>
-      <c r="G1" s="333"/>
-      <c r="H1" s="333"/>
-      <c r="I1" s="333"/>
-      <c r="J1" s="333"/>
-      <c r="K1" s="333"/>
-      <c r="L1" s="333"/>
-      <c r="M1" s="333"/>
-      <c r="N1" s="333"/>
-      <c r="O1" s="333"/>
-      <c r="P1" s="333"/>
-      <c r="Q1" s="333"/>
-      <c r="R1" s="333"/>
-      <c r="S1" s="333"/>
-      <c r="T1" s="333"/>
-      <c r="U1" s="333"/>
-      <c r="V1" s="333"/>
-      <c r="W1" s="333"/>
-      <c r="X1" s="333"/>
-      <c r="Y1" s="333"/>
+      <c r="C1" s="304"/>
+      <c r="D1" s="304"/>
+      <c r="E1" s="304"/>
+      <c r="F1" s="304"/>
+      <c r="G1" s="304"/>
+      <c r="H1" s="304"/>
+      <c r="I1" s="304"/>
+      <c r="J1" s="304"/>
+      <c r="K1" s="304"/>
+      <c r="L1" s="304"/>
+      <c r="M1" s="304"/>
+      <c r="N1" s="304"/>
+      <c r="O1" s="304"/>
+      <c r="P1" s="304"/>
+      <c r="Q1" s="304"/>
+      <c r="R1" s="304"/>
+      <c r="S1" s="304"/>
+      <c r="T1" s="304"/>
+      <c r="U1" s="304"/>
+      <c r="V1" s="304"/>
+      <c r="W1" s="304"/>
+      <c r="X1" s="304"/>
+      <c r="Y1" s="304"/>
       <c r="Z1" s="22"/>
       <c r="AA1" s="238" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="8" customFormat="1" ht="108">
+    <row r="2" spans="1:28" s="8" customFormat="1" ht="101">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -3825,7 +3898,7 @@
         <v>Vendor 7</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="30" customHeight="1">
+    <row r="5" spans="1:28" ht="78">
       <c r="A5" s="21" t="s">
         <v>2</v>
       </c>
@@ -3976,7 +4049,7 @@
         <v>Vendor 9</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="30" customHeight="1">
+    <row r="7" spans="1:28" ht="52">
       <c r="A7" s="21" t="s">
         <v>2</v>
       </c>
@@ -4042,7 +4115,7 @@
         <v>Vendor 10</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="30" customHeight="1">
+    <row r="8" spans="1:28" ht="52">
       <c r="A8" s="21" t="s">
         <v>2</v>
       </c>
@@ -4106,7 +4179,7 @@
         <v>Vendor 1</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="30" customHeight="1">
+    <row r="9" spans="1:28" ht="52">
       <c r="A9" s="21" t="s">
         <v>2</v>
       </c>
@@ -4170,7 +4243,7 @@
         <v>Vendor 10</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="30" customHeight="1">
+    <row r="10" spans="1:28" ht="52">
       <c r="A10" s="21" t="s">
         <v>2</v>
       </c>
@@ -4234,7 +4307,7 @@
         <v>Vendor 1</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="30" customHeight="1">
+    <row r="11" spans="1:28" ht="52">
       <c r="A11" s="21" t="s">
         <v>2</v>
       </c>
@@ -4300,7 +4373,7 @@
         <v>Vendor 1</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="30" customHeight="1">
+    <row r="12" spans="1:28" ht="52">
       <c r="A12" s="21" t="s">
         <v>2</v>
       </c>
@@ -4366,7 +4439,7 @@
         <v>Vendor 1</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="30" customHeight="1">
+    <row r="13" spans="1:28" ht="52">
       <c r="A13" s="21" t="s">
         <v>2</v>
       </c>
@@ -4430,7 +4503,7 @@
         <v>Vendor 1</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="30" customHeight="1">
+    <row r="14" spans="1:28" ht="52">
       <c r="A14" s="21" t="s">
         <v>2</v>
       </c>
@@ -5222,55 +5295,55 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="74" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" style="64" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.85546875" style="4" customWidth="1"/>
-    <col min="21" max="21" width="85.5703125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="118.7109375" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.7109375" style="1"/>
+    <col min="8" max="8" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" style="64" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.83203125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="85.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="118.6640625" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="24" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B1" s="335" t="s">
+      <c r="B1" s="306" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="335"/>
-      <c r="D1" s="335"/>
-      <c r="E1" s="335"/>
-      <c r="F1" s="335"/>
-      <c r="G1" s="335"/>
-      <c r="H1" s="335"/>
-      <c r="I1" s="335"/>
-      <c r="J1" s="335"/>
-      <c r="K1" s="335"/>
-      <c r="L1" s="335"/>
-      <c r="M1" s="335"/>
-      <c r="N1" s="335"/>
-      <c r="O1" s="335"/>
-      <c r="P1" s="335"/>
-      <c r="Q1" s="335"/>
-      <c r="R1" s="335"/>
-      <c r="S1" s="335"/>
-      <c r="T1" s="335"/>
+      <c r="C1" s="306"/>
+      <c r="D1" s="306"/>
+      <c r="E1" s="306"/>
+      <c r="F1" s="306"/>
+      <c r="G1" s="306"/>
+      <c r="H1" s="306"/>
+      <c r="I1" s="306"/>
+      <c r="J1" s="306"/>
+      <c r="K1" s="306"/>
+      <c r="L1" s="306"/>
+      <c r="M1" s="306"/>
+      <c r="N1" s="306"/>
+      <c r="O1" s="306"/>
+      <c r="P1" s="306"/>
+      <c r="Q1" s="306"/>
+      <c r="R1" s="306"/>
+      <c r="S1" s="306"/>
+      <c r="T1" s="306"/>
       <c r="U1" s="254" t="s">
         <v>47</v>
       </c>
@@ -5280,7 +5353,7 @@
       <c r="Y1" s="69"/>
       <c r="AA1" s="23"/>
     </row>
-    <row r="2" spans="1:27" s="60" customFormat="1" ht="105.6">
+    <row r="2" spans="1:27" s="60" customFormat="1" ht="105">
       <c r="B2" s="57" t="s">
         <v>3</v>
       </c>
@@ -5345,7 +5418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="3" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A3" s="2" t="s">
         <v>64</v>
       </c>
@@ -5391,7 +5464,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="4" spans="1:27" s="2" customFormat="1" ht="25">
       <c r="A4" s="2" t="s">
         <v>64</v>
       </c>
@@ -5430,7 +5503,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="5" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5488,7 +5561,7 @@
         <v>vendor 6</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="6" spans="1:27" s="2" customFormat="1" ht="25">
       <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
@@ -5542,7 +5615,7 @@
         <v>vendor 6</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="7" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
@@ -5598,7 +5671,7 @@
         <v>vendor 13</v>
       </c>
     </row>
-    <row r="8" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="8" spans="1:27" s="2" customFormat="1" ht="25">
       <c r="A8" s="2" t="s">
         <v>64</v>
       </c>
@@ -5652,7 +5725,7 @@
         <v>vendor 13</v>
       </c>
     </row>
-    <row r="9" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="9" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -5710,7 +5783,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="10" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="10" spans="1:27" s="2" customFormat="1" ht="25">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
@@ -5764,7 +5837,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="11" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -5822,7 +5895,7 @@
         <v>vendor 6</v>
       </c>
     </row>
-    <row r="12" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="12" spans="1:27" s="2" customFormat="1" ht="25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -5876,7 +5949,7 @@
         <v>vendor 6</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="13" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A13" s="2" t="s">
         <v>64</v>
       </c>
@@ -5935,7 +6008,7 @@
         <v>vendor 1</v>
       </c>
     </row>
-    <row r="14" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="14" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
@@ -5981,7 +6054,7 @@
         <v>vendor 6</v>
       </c>
     </row>
-    <row r="15" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="15" spans="1:27" s="2" customFormat="1" ht="25">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -6023,7 +6096,7 @@
         <v>vendor 6</v>
       </c>
     </row>
-    <row r="16" spans="1:27" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="16" spans="1:27" s="2" customFormat="1" ht="26">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -6077,7 +6150,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="17" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -6127,7 +6200,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="18" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
@@ -6177,7 +6250,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="19" spans="1:21" s="2" customFormat="1" ht="26">
       <c r="A19" s="2" t="s">
         <v>64</v>
       </c>
@@ -6231,7 +6304,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="20" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
@@ -6281,7 +6354,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="21" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -6331,7 +6404,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="22" spans="1:21" s="2" customFormat="1" ht="26">
       <c r="A22" s="2" t="s">
         <v>64</v>
       </c>
@@ -6383,7 +6456,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="23" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
@@ -6431,7 +6504,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="24" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A24" s="2" t="s">
         <v>64</v>
       </c>
@@ -6479,7 +6552,7 @@
         <v>vendor 14</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="25" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A25" s="2" t="s">
         <v>64</v>
       </c>
@@ -6527,7 +6600,7 @@
         <v>vendor 14</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="26" spans="1:21" s="2" customFormat="1" ht="26">
       <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
@@ -6575,7 +6648,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="27" spans="1:21" s="2" customFormat="1" ht="26">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -6633,7 +6706,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="28" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
@@ -6687,7 +6760,7 @@
         <v>vendor 3</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="29" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A29" s="2" t="s">
         <v>64</v>
       </c>
@@ -6741,7 +6814,7 @@
         <v>vendor 7</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="30" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -6795,7 +6868,7 @@
         <v>vendor 7</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="31" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A31" s="2" t="s">
         <v>64</v>
       </c>
@@ -6849,7 +6922,7 @@
         <v>vendor 7</v>
       </c>
     </row>
-    <row r="32" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="32" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A32" s="2" t="s">
         <v>64</v>
       </c>
@@ -6903,7 +6976,7 @@
         <v>vendor 7</v>
       </c>
     </row>
-    <row r="33" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="33" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
@@ -6957,7 +7030,7 @@
         <v>vendor 7</v>
       </c>
     </row>
-    <row r="34" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="34" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A34" s="2" t="s">
         <v>64</v>
       </c>
@@ -7011,7 +7084,7 @@
         <v>vendor 7</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="35" spans="1:21" s="2" customFormat="1" ht="26">
       <c r="A35" s="2" t="s">
         <v>64</v>
       </c>
@@ -7059,7 +7132,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="36" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A36" s="2" t="s">
         <v>64</v>
       </c>
@@ -7103,7 +7176,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="37" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="37" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
@@ -7147,7 +7220,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="38" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="38" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A38" s="2" t="s">
         <v>64</v>
       </c>
@@ -7191,7 +7264,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="39" spans="1:21" s="2" customFormat="1" ht="35.450000000000003">
+    <row r="39" spans="1:21" s="2" customFormat="1" ht="25">
       <c r="A39" s="2" t="s">
         <v>64</v>
       </c>
@@ -7235,52 +7308,52 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="51" customFormat="1" ht="35.450000000000003">
+    <row r="40" spans="1:21" s="51" customFormat="1" ht="25">
       <c r="B40" s="52"/>
-      <c r="C40" s="334" t="s">
+      <c r="C40" s="305" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="334"/>
-      <c r="E40" s="334"/>
-      <c r="F40" s="334"/>
-      <c r="G40" s="334"/>
-      <c r="H40" s="334"/>
-      <c r="I40" s="334"/>
-      <c r="J40" s="334"/>
-      <c r="K40" s="334"/>
-      <c r="L40" s="334"/>
-      <c r="M40" s="334"/>
-      <c r="N40" s="334"/>
-      <c r="O40" s="334"/>
-      <c r="P40" s="334"/>
-      <c r="Q40" s="334"/>
-      <c r="R40" s="334"/>
-      <c r="S40" s="334"/>
-      <c r="T40" s="334"/>
-      <c r="U40" s="334"/>
-    </row>
-    <row r="41" spans="1:21" ht="35.450000000000003">
-      <c r="C41" s="334" t="s">
+      <c r="D40" s="305"/>
+      <c r="E40" s="305"/>
+      <c r="F40" s="305"/>
+      <c r="G40" s="305"/>
+      <c r="H40" s="305"/>
+      <c r="I40" s="305"/>
+      <c r="J40" s="305"/>
+      <c r="K40" s="305"/>
+      <c r="L40" s="305"/>
+      <c r="M40" s="305"/>
+      <c r="N40" s="305"/>
+      <c r="O40" s="305"/>
+      <c r="P40" s="305"/>
+      <c r="Q40" s="305"/>
+      <c r="R40" s="305"/>
+      <c r="S40" s="305"/>
+      <c r="T40" s="305"/>
+      <c r="U40" s="305"/>
+    </row>
+    <row r="41" spans="1:21" ht="25">
+      <c r="C41" s="305" t="s">
         <v>81</v>
       </c>
-      <c r="D41" s="334"/>
-      <c r="E41" s="334"/>
-      <c r="F41" s="334"/>
-      <c r="G41" s="334"/>
-      <c r="H41" s="334"/>
-      <c r="I41" s="334"/>
-      <c r="J41" s="334"/>
-      <c r="K41" s="334"/>
-      <c r="L41" s="334"/>
-      <c r="M41" s="334"/>
-      <c r="N41" s="334"/>
-      <c r="O41" s="334"/>
-      <c r="P41" s="334"/>
-      <c r="Q41" s="334"/>
-      <c r="R41" s="334"/>
-      <c r="S41" s="334"/>
-      <c r="T41" s="334"/>
-      <c r="U41" s="334"/>
+      <c r="D41" s="305"/>
+      <c r="E41" s="305"/>
+      <c r="F41" s="305"/>
+      <c r="G41" s="305"/>
+      <c r="H41" s="305"/>
+      <c r="I41" s="305"/>
+      <c r="J41" s="305"/>
+      <c r="K41" s="305"/>
+      <c r="L41" s="305"/>
+      <c r="M41" s="305"/>
+      <c r="N41" s="305"/>
+      <c r="O41" s="305"/>
+      <c r="P41" s="305"/>
+      <c r="Q41" s="305"/>
+      <c r="R41" s="305"/>
+      <c r="S41" s="305"/>
+      <c r="T41" s="305"/>
+      <c r="U41" s="305"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7301,32 +7374,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="35.450000000000003"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="19" style="74" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="90" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="82.42578125" style="70" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" style="74" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="90" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="82.5" style="70" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.5" style="74" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="74" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" style="74" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="74" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" style="74" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.5703125" style="74" customWidth="1"/>
-    <col min="16" max="16" width="255.5703125" style="74" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.42578125" style="74"/>
+    <col min="10" max="10" width="10.83203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" style="74" customWidth="1"/>
+    <col min="14" max="14" width="18.1640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.5" style="74" customWidth="1"/>
+    <col min="16" max="16" width="255.5" style="74" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.5" style="74"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="257" customFormat="1" ht="45" customHeight="1">
-      <c r="B1" s="346" t="s">
+      <c r="B1" s="317" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="346"/>
+      <c r="C1" s="317"/>
       <c r="D1" s="258"/>
       <c r="E1" s="259"/>
       <c r="F1" s="259"/>
@@ -7342,7 +7414,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="73" customFormat="1" ht="106.5">
+    <row r="2" spans="1:24" s="73" customFormat="1" ht="101">
       <c r="A2" s="70" t="s">
         <v>84</v>
       </c>
@@ -7405,7 +7477,7 @@
       <c r="B3" s="75">
         <v>1</v>
       </c>
-      <c r="C3" s="344" t="s">
+      <c r="C3" s="315" t="s">
         <v>86</v>
       </c>
       <c r="D3" s="92" t="s">
@@ -7452,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="B4" s="77"/>
-      <c r="C4" s="345"/>
+      <c r="C4" s="316"/>
       <c r="D4" s="92" t="s">
         <v>89</v>
       </c>
@@ -7497,7 +7569,7 @@
         <v>84</v>
       </c>
       <c r="B5" s="77"/>
-      <c r="C5" s="345"/>
+      <c r="C5" s="316"/>
       <c r="D5" s="92" t="s">
         <v>91</v>
       </c>
@@ -7542,7 +7614,7 @@
         <v>84</v>
       </c>
       <c r="B6" s="77"/>
-      <c r="C6" s="345"/>
+      <c r="C6" s="316"/>
       <c r="D6" s="92" t="s">
         <v>93</v>
       </c>
@@ -7586,7 +7658,7 @@
         <v>84</v>
       </c>
       <c r="B7" s="77"/>
-      <c r="C7" s="345"/>
+      <c r="C7" s="316"/>
       <c r="D7" s="92" t="s">
         <v>95</v>
       </c>
@@ -7630,7 +7702,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="77"/>
-      <c r="C8" s="345"/>
+      <c r="C8" s="316"/>
       <c r="D8" s="92" t="s">
         <v>97</v>
       </c>
@@ -7674,7 +7746,7 @@
         <v>84</v>
       </c>
       <c r="B9" s="77"/>
-      <c r="C9" s="345"/>
+      <c r="C9" s="316"/>
       <c r="D9" s="92" t="s">
         <v>99</v>
       </c>
@@ -7722,7 +7794,7 @@
       <c r="B10" s="78">
         <v>2</v>
       </c>
-      <c r="C10" s="343" t="s">
+      <c r="C10" s="314" t="s">
         <v>101</v>
       </c>
       <c r="D10" s="92" t="s">
@@ -7767,7 +7839,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="79"/>
-      <c r="C11" s="342"/>
+      <c r="C11" s="313"/>
       <c r="D11" s="92" t="s">
         <v>89</v>
       </c>
@@ -7810,7 +7882,7 @@
         <v>84</v>
       </c>
       <c r="B12" s="79"/>
-      <c r="C12" s="342"/>
+      <c r="C12" s="313"/>
       <c r="D12" s="92" t="s">
         <v>91</v>
       </c>
@@ -7853,7 +7925,7 @@
         <v>84</v>
       </c>
       <c r="B13" s="79"/>
-      <c r="C13" s="342"/>
+      <c r="C13" s="313"/>
       <c r="D13" s="92" t="s">
         <v>93</v>
       </c>
@@ -7898,7 +7970,7 @@
         <v>84</v>
       </c>
       <c r="B14" s="79"/>
-      <c r="C14" s="342"/>
+      <c r="C14" s="313"/>
       <c r="D14" s="92" t="s">
         <v>95</v>
       </c>
@@ -7941,7 +8013,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="79"/>
-      <c r="C15" s="342"/>
+      <c r="C15" s="313"/>
       <c r="D15" s="92" t="s">
         <v>97</v>
       </c>
@@ -8030,7 +8102,7 @@
       <c r="B17" s="75">
         <v>3.1</v>
       </c>
-      <c r="C17" s="343" t="s">
+      <c r="C17" s="314" t="s">
         <v>104</v>
       </c>
       <c r="D17" s="93">
@@ -8072,7 +8144,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="77"/>
-      <c r="C18" s="342"/>
+      <c r="C18" s="313"/>
       <c r="D18" s="93">
         <v>200</v>
       </c>
@@ -8112,7 +8184,7 @@
         <v>84</v>
       </c>
       <c r="B19" s="77"/>
-      <c r="C19" s="342"/>
+      <c r="C19" s="313"/>
       <c r="D19" s="93">
         <v>300</v>
       </c>
@@ -8152,7 +8224,7 @@
         <v>84</v>
       </c>
       <c r="B20" s="77"/>
-      <c r="C20" s="347"/>
+      <c r="C20" s="318"/>
       <c r="D20" s="93" t="s">
         <v>105</v>
       </c>
@@ -8199,7 +8271,7 @@
       <c r="B21" s="81">
         <v>4</v>
       </c>
-      <c r="C21" s="348" t="s">
+      <c r="C21" s="319" t="s">
         <v>107</v>
       </c>
       <c r="D21" s="92" t="s">
@@ -8244,7 +8316,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="82"/>
-      <c r="C22" s="349"/>
+      <c r="C22" s="320"/>
       <c r="D22" s="92" t="s">
         <v>89</v>
       </c>
@@ -8287,7 +8359,7 @@
         <v>84</v>
       </c>
       <c r="B23" s="82"/>
-      <c r="C23" s="349"/>
+      <c r="C23" s="320"/>
       <c r="D23" s="92" t="s">
         <v>91</v>
       </c>
@@ -8330,7 +8402,7 @@
         <v>84</v>
       </c>
       <c r="B24" s="82"/>
-      <c r="C24" s="349"/>
+      <c r="C24" s="320"/>
       <c r="D24" s="92" t="s">
         <v>93</v>
       </c>
@@ -8373,7 +8445,7 @@
         <v>84</v>
       </c>
       <c r="B25" s="82"/>
-      <c r="C25" s="349"/>
+      <c r="C25" s="320"/>
       <c r="D25" s="92" t="s">
         <v>95</v>
       </c>
@@ -8416,7 +8488,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="82"/>
-      <c r="C26" s="349"/>
+      <c r="C26" s="320"/>
       <c r="D26" s="92" t="s">
         <v>97</v>
       </c>
@@ -8459,7 +8531,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="84"/>
-      <c r="C27" s="350"/>
+      <c r="C27" s="321"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
@@ -8499,7 +8571,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" ht="26">
       <c r="A28" s="74" t="s">
         <v>84</v>
       </c>
@@ -8546,7 +8618,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="36.950000000000003" customHeight="1">
+    <row r="29" spans="1:16" ht="37" customHeight="1">
       <c r="A29" s="74" t="s">
         <v>84</v>
       </c>
@@ -8591,7 +8663,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" ht="26">
       <c r="A30" s="74" t="s">
         <v>84</v>
       </c>
@@ -8636,7 +8708,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" ht="26">
       <c r="A31" s="74" t="s">
         <v>84</v>
       </c>
@@ -8681,7 +8753,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" ht="26">
       <c r="A32" s="74" t="s">
         <v>84</v>
       </c>
@@ -8728,7 +8800,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" ht="26">
       <c r="A33" s="74" t="s">
         <v>84</v>
       </c>
@@ -8773,7 +8845,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" ht="26">
       <c r="A34" s="74" t="s">
         <v>84</v>
       </c>
@@ -8825,7 +8897,7 @@
       <c r="B35" s="75">
         <v>6</v>
       </c>
-      <c r="C35" s="344" t="s">
+      <c r="C35" s="315" t="s">
         <v>117</v>
       </c>
       <c r="D35" s="92" t="s">
@@ -8866,7 +8938,7 @@
         <v>84</v>
       </c>
       <c r="B36" s="77"/>
-      <c r="C36" s="345"/>
+      <c r="C36" s="316"/>
       <c r="D36" s="92" t="s">
         <v>89</v>
       </c>
@@ -8907,7 +8979,7 @@
         <v>84</v>
       </c>
       <c r="B37" s="77"/>
-      <c r="C37" s="345"/>
+      <c r="C37" s="316"/>
       <c r="D37" s="92" t="s">
         <v>91</v>
       </c>
@@ -8948,7 +9020,7 @@
         <v>84</v>
       </c>
       <c r="B38" s="77"/>
-      <c r="C38" s="345"/>
+      <c r="C38" s="316"/>
       <c r="D38" s="92" t="s">
         <v>93</v>
       </c>
@@ -9116,7 +9188,7 @@
       <c r="B42" s="78">
         <v>7</v>
       </c>
-      <c r="C42" s="343" t="s">
+      <c r="C42" s="314" t="s">
         <v>119</v>
       </c>
       <c r="D42" s="92" t="s">
@@ -9159,7 +9231,7 @@
         <v>84</v>
       </c>
       <c r="B43" s="79"/>
-      <c r="C43" s="342"/>
+      <c r="C43" s="313"/>
       <c r="D43" s="92" t="s">
         <v>89</v>
       </c>
@@ -9202,7 +9274,7 @@
         <v>84</v>
       </c>
       <c r="B44" s="79"/>
-      <c r="C44" s="342"/>
+      <c r="C44" s="313"/>
       <c r="D44" s="92" t="s">
         <v>91</v>
       </c>
@@ -9245,7 +9317,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="79"/>
-      <c r="C45" s="342"/>
+      <c r="C45" s="313"/>
       <c r="D45" s="92" t="s">
         <v>93</v>
       </c>
@@ -9288,7 +9360,7 @@
         <v>84</v>
       </c>
       <c r="B46" s="79"/>
-      <c r="C46" s="342"/>
+      <c r="C46" s="313"/>
       <c r="D46" s="92" t="s">
         <v>95</v>
       </c>
@@ -9331,7 +9403,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="79"/>
-      <c r="C47" s="342"/>
+      <c r="C47" s="313"/>
       <c r="D47" s="92" t="s">
         <v>97</v>
       </c>
@@ -9464,7 +9536,7 @@
       <c r="B50" s="79">
         <v>8</v>
       </c>
-      <c r="C50" s="342" t="s">
+      <c r="C50" s="313" t="s">
         <v>121</v>
       </c>
       <c r="D50" s="229" t="s">
@@ -9494,7 +9566,7 @@
         <v>84</v>
       </c>
       <c r="B51" s="79"/>
-      <c r="C51" s="342"/>
+      <c r="C51" s="313"/>
       <c r="D51" s="92" t="s">
         <v>89</v>
       </c>
@@ -9522,7 +9594,7 @@
         <v>84</v>
       </c>
       <c r="B52" s="79"/>
-      <c r="C52" s="342"/>
+      <c r="C52" s="313"/>
       <c r="D52" s="92" t="s">
         <v>91</v>
       </c>
@@ -9550,7 +9622,7 @@
         <v>84</v>
       </c>
       <c r="B53" s="79"/>
-      <c r="C53" s="342"/>
+      <c r="C53" s="313"/>
       <c r="D53" s="92" t="s">
         <v>93</v>
       </c>
@@ -9578,7 +9650,7 @@
         <v>84</v>
       </c>
       <c r="B54" s="79"/>
-      <c r="C54" s="342"/>
+      <c r="C54" s="313"/>
       <c r="D54" s="92" t="s">
         <v>95</v>
       </c>
@@ -9606,7 +9678,7 @@
         <v>84</v>
       </c>
       <c r="B55" s="79"/>
-      <c r="C55" s="342"/>
+      <c r="C55" s="313"/>
       <c r="D55" s="92" t="s">
         <v>97</v>
       </c>
@@ -9657,7 +9729,7 @@
         <v>Vendor 9</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="35.450000000000003" customHeight="1">
+    <row r="57" spans="1:23" ht="35.5" customHeight="1">
       <c r="A57" s="74" t="s">
         <v>84</v>
       </c>
@@ -9693,12 +9765,12 @@
       <c r="M57" s="76">
         <v>15</v>
       </c>
-      <c r="N57" s="336" t="s">
+      <c r="N57" s="307" t="s">
         <v>123</v>
       </c>
-      <c r="O57" s="337"/>
-    </row>
-    <row r="58" spans="1:23">
+      <c r="O57" s="308"/>
+    </row>
+    <row r="58" spans="1:23" ht="26">
       <c r="A58" s="74" t="s">
         <v>84</v>
       </c>
@@ -9736,10 +9808,10 @@
       <c r="M58" s="76">
         <v>20</v>
       </c>
-      <c r="N58" s="338"/>
-      <c r="O58" s="339"/>
-    </row>
-    <row r="59" spans="1:23">
+      <c r="N58" s="309"/>
+      <c r="O58" s="310"/>
+    </row>
+    <row r="59" spans="1:23" ht="26">
       <c r="A59" s="74" t="s">
         <v>84</v>
       </c>
@@ -9775,10 +9847,10 @@
       <c r="M59" s="76">
         <v>25</v>
       </c>
-      <c r="N59" s="338"/>
-      <c r="O59" s="339"/>
-    </row>
-    <row r="60" spans="1:23">
+      <c r="N59" s="309"/>
+      <c r="O59" s="310"/>
+    </row>
+    <row r="60" spans="1:23" ht="26">
       <c r="A60" s="74" t="s">
         <v>84</v>
       </c>
@@ -9814,8 +9886,8 @@
       <c r="M60" s="76">
         <v>30</v>
       </c>
-      <c r="N60" s="338"/>
-      <c r="O60" s="339"/>
+      <c r="N60" s="309"/>
+      <c r="O60" s="310"/>
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="74" t="s">
@@ -9851,8 +9923,8 @@
       <c r="M61" s="76">
         <v>15</v>
       </c>
-      <c r="N61" s="338"/>
-      <c r="O61" s="339"/>
+      <c r="N61" s="309"/>
+      <c r="O61" s="310"/>
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="74" t="s">
@@ -9888,8 +9960,8 @@
       <c r="M62" s="76">
         <v>15</v>
       </c>
-      <c r="N62" s="338"/>
-      <c r="O62" s="339"/>
+      <c r="N62" s="309"/>
+      <c r="O62" s="310"/>
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="74" t="s">
@@ -9925,8 +9997,8 @@
       <c r="M63" s="76">
         <v>15</v>
       </c>
-      <c r="N63" s="338"/>
-      <c r="O63" s="339"/>
+      <c r="N63" s="309"/>
+      <c r="O63" s="310"/>
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="74" t="s">
@@ -9962,8 +10034,8 @@
       <c r="M64" s="76">
         <v>15</v>
       </c>
-      <c r="N64" s="340"/>
-      <c r="O64" s="341"/>
+      <c r="N64" s="311"/>
+      <c r="O64" s="312"/>
     </row>
     <row r="65" spans="2:15">
       <c r="D65" s="91"/>
@@ -10009,47 +10081,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AV287"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="35.450000000000003"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="109"/>
-    <col min="2" max="2" width="15.85546875" style="109" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="109" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="131" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="134" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="109" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="109"/>
+    <col min="2" max="2" width="15.83203125" style="109" customWidth="1"/>
+    <col min="3" max="3" width="54.33203125" style="109" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="131" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" style="134" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="109" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="23" style="109" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" style="135" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" style="135" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="109" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="109" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="109" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="109" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" style="109" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" style="109" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" style="109" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" style="109" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" style="109" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5" style="109" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" style="109" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="109" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="109" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5" style="109" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.1640625" style="109" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18" style="109" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="78.28515625" style="136" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.85546875" style="109" customWidth="1"/>
-    <col min="22" max="23" width="8.7109375" style="109"/>
-    <col min="24" max="24" width="8.7109375" style="109" customWidth="1"/>
-    <col min="25" max="16384" width="8.7109375" style="109"/>
+    <col min="20" max="20" width="78.33203125" style="136" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="35.83203125" style="109" customWidth="1"/>
+    <col min="22" max="23" width="8.6640625" style="109"/>
+    <col min="24" max="24" width="8.6640625" style="109" customWidth="1"/>
+    <col min="25" max="16384" width="8.6640625" style="109"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" s="266" customFormat="1" ht="40.5" customHeight="1">
-      <c r="B1" s="359" t="s">
+      <c r="B1" s="324" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="359"/>
-      <c r="D1" s="359"/>
+      <c r="C1" s="324"/>
+      <c r="D1" s="324"/>
       <c r="E1" s="267"/>
       <c r="H1" s="267"/>
       <c r="T1" s="268" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:48" s="96" customFormat="1" ht="191.1" customHeight="1">
+    <row r="2" spans="1:48" s="96" customFormat="1" ht="191" customHeight="1">
       <c r="B2" s="57" t="s">
         <v>3</v>
       </c>
@@ -10098,10 +10170,10 @@
       <c r="Q2" s="260" t="s">
         <v>145</v>
       </c>
-      <c r="R2" s="357" t="s">
+      <c r="R2" s="322" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="358"/>
+      <c r="S2" s="323"/>
       <c r="T2" s="56" t="s">
         <v>24</v>
       </c>
@@ -10159,7 +10231,7 @@
         <v>vendor2</v>
       </c>
     </row>
-    <row r="4" spans="1:48" ht="38.450000000000003" customHeight="1">
+    <row r="4" spans="1:48" ht="38.5" customHeight="1">
       <c r="A4" s="97" t="s">
         <v>146</v>
       </c>
@@ -10213,38 +10285,38 @@
       <c r="T4" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="U4" s="364" t="s">
+      <c r="U4" s="329" t="s">
         <v>151</v>
       </c>
-      <c r="V4" s="365"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="365"/>
-      <c r="Z4" s="365"/>
-      <c r="AA4" s="365"/>
-      <c r="AB4" s="365"/>
-      <c r="AC4" s="365"/>
-      <c r="AD4" s="365"/>
-      <c r="AE4" s="365"/>
-      <c r="AF4" s="365"/>
-      <c r="AG4" s="365"/>
-      <c r="AH4" s="365"/>
-      <c r="AI4" s="365"/>
-      <c r="AJ4" s="365"/>
-      <c r="AK4" s="365"/>
-      <c r="AL4" s="365"/>
-      <c r="AM4" s="365"/>
-      <c r="AN4" s="365"/>
-      <c r="AO4" s="365"/>
-      <c r="AP4" s="365"/>
-      <c r="AQ4" s="365"/>
-      <c r="AR4" s="365"/>
-      <c r="AS4" s="365"/>
-      <c r="AT4" s="365"/>
-      <c r="AU4" s="365"/>
-      <c r="AV4" s="365"/>
-    </row>
-    <row r="5" spans="1:48">
+      <c r="V4" s="330"/>
+      <c r="W4" s="330"/>
+      <c r="X4" s="330"/>
+      <c r="Y4" s="330"/>
+      <c r="Z4" s="330"/>
+      <c r="AA4" s="330"/>
+      <c r="AB4" s="330"/>
+      <c r="AC4" s="330"/>
+      <c r="AD4" s="330"/>
+      <c r="AE4" s="330"/>
+      <c r="AF4" s="330"/>
+      <c r="AG4" s="330"/>
+      <c r="AH4" s="330"/>
+      <c r="AI4" s="330"/>
+      <c r="AJ4" s="330"/>
+      <c r="AK4" s="330"/>
+      <c r="AL4" s="330"/>
+      <c r="AM4" s="330"/>
+      <c r="AN4" s="330"/>
+      <c r="AO4" s="330"/>
+      <c r="AP4" s="330"/>
+      <c r="AQ4" s="330"/>
+      <c r="AR4" s="330"/>
+      <c r="AS4" s="330"/>
+      <c r="AT4" s="330"/>
+      <c r="AU4" s="330"/>
+      <c r="AV4" s="330"/>
+    </row>
+    <row r="5" spans="1:48" ht="26">
       <c r="A5" s="97" t="s">
         <v>146</v>
       </c>
@@ -10293,7 +10365,7 @@
         <v>vendor4</v>
       </c>
     </row>
-    <row r="6" spans="1:48" s="117" customFormat="1">
+    <row r="6" spans="1:48" s="117" customFormat="1" ht="26">
       <c r="A6" s="97" t="s">
         <v>146</v>
       </c>
@@ -10340,7 +10412,7 @@
       <c r="U6" s="109"/>
       <c r="V6" s="109"/>
     </row>
-    <row r="7" spans="1:48" s="117" customFormat="1">
+    <row r="7" spans="1:48" s="117" customFormat="1" ht="26">
       <c r="A7" s="97" t="s">
         <v>146</v>
       </c>
@@ -10387,7 +10459,7 @@
       <c r="U7" s="109"/>
       <c r="V7" s="109"/>
     </row>
-    <row r="8" spans="1:48" s="117" customFormat="1">
+    <row r="8" spans="1:48" s="117" customFormat="1" ht="26">
       <c r="A8" s="97" t="s">
         <v>146</v>
       </c>
@@ -10438,7 +10510,7 @@
       <c r="V8" s="109"/>
       <c r="W8" s="109"/>
     </row>
-    <row r="9" spans="1:48" s="117" customFormat="1" ht="71.45" customHeight="1">
+    <row r="9" spans="1:48" s="117" customFormat="1" ht="71.5" customHeight="1">
       <c r="A9" s="97" t="s">
         <v>146</v>
       </c>
@@ -10487,7 +10559,7 @@
       <c r="V9" s="109"/>
       <c r="W9" s="109"/>
     </row>
-    <row r="10" spans="1:48" s="117" customFormat="1">
+    <row r="10" spans="1:48" s="117" customFormat="1" ht="26">
       <c r="A10" s="97" t="s">
         <v>146</v>
       </c>
@@ -10536,7 +10608,7 @@
       <c r="U10" s="109"/>
       <c r="V10" s="109"/>
     </row>
-    <row r="11" spans="1:48" s="117" customFormat="1" ht="33.6" customHeight="1">
+    <row r="11" spans="1:48" s="117" customFormat="1" ht="33.5" customHeight="1">
       <c r="A11" s="97" t="s">
         <v>146</v>
       </c>
@@ -10587,10 +10659,10 @@
       <c r="A12" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="327">
+      <c r="B12" s="331">
         <v>7</v>
       </c>
-      <c r="C12" s="354" t="s">
+      <c r="C12" s="336" t="s">
         <v>160</v>
       </c>
       <c r="D12" s="115">
@@ -10634,8 +10706,8 @@
       <c r="A13" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B13" s="351"/>
-      <c r="C13" s="355"/>
+      <c r="B13" s="332"/>
+      <c r="C13" s="337"/>
       <c r="D13" s="115">
         <v>20</v>
       </c>
@@ -10677,8 +10749,8 @@
       <c r="A14" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B14" s="351"/>
-      <c r="C14" s="355"/>
+      <c r="B14" s="332"/>
+      <c r="C14" s="337"/>
       <c r="D14" s="115">
         <v>30</v>
       </c>
@@ -10720,8 +10792,8 @@
       <c r="A15" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B15" s="351"/>
-      <c r="C15" s="355"/>
+      <c r="B15" s="332"/>
+      <c r="C15" s="337"/>
       <c r="D15" s="115">
         <v>40</v>
       </c>
@@ -10763,8 +10835,8 @@
       <c r="A16" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="324"/>
-      <c r="C16" s="356"/>
+      <c r="B16" s="335"/>
+      <c r="C16" s="338"/>
       <c r="D16" s="115">
         <v>50</v>
       </c>
@@ -10802,7 +10874,7 @@
       <c r="U16" s="109"/>
       <c r="V16" s="109"/>
     </row>
-    <row r="17" spans="1:22" s="117" customFormat="1">
+    <row r="17" spans="1:22" s="117" customFormat="1" ht="26">
       <c r="A17" s="97" t="s">
         <v>146</v>
       </c>
@@ -10853,10 +10925,10 @@
       <c r="A18" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="327">
+      <c r="B18" s="331">
         <v>9</v>
       </c>
-      <c r="C18" s="354" t="s">
+      <c r="C18" s="336" t="s">
         <v>162</v>
       </c>
       <c r="D18" s="115">
@@ -10900,8 +10972,8 @@
       <c r="A19" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B19" s="324"/>
-      <c r="C19" s="356"/>
+      <c r="B19" s="335"/>
+      <c r="C19" s="338"/>
       <c r="D19" s="115">
         <v>100</v>
       </c>
@@ -10941,14 +11013,14 @@
       <c r="U19" s="109"/>
       <c r="V19" s="109"/>
     </row>
-    <row r="20" spans="1:22" ht="39.6" customHeight="1">
+    <row r="20" spans="1:22" ht="39.5" customHeight="1">
       <c r="A20" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="360">
+      <c r="B20" s="325">
         <v>10</v>
       </c>
-      <c r="C20" s="362" t="s">
+      <c r="C20" s="327" t="s">
         <v>163</v>
       </c>
       <c r="D20" s="115" t="s">
@@ -10992,8 +11064,8 @@
       <c r="A21" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="361"/>
-      <c r="C21" s="363"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="328"/>
       <c r="D21" s="115"/>
       <c r="E21" s="103"/>
       <c r="F21" s="103"/>
@@ -11033,10 +11105,10 @@
       <c r="A22" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="327">
+      <c r="B22" s="331">
         <v>11</v>
       </c>
-      <c r="C22" s="352" t="s">
+      <c r="C22" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D22" s="122">
@@ -11080,8 +11152,8 @@
       <c r="A23" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="351"/>
-      <c r="C23" s="353"/>
+      <c r="B23" s="332"/>
+      <c r="C23" s="334"/>
       <c r="D23" s="122">
         <v>200</v>
       </c>
@@ -11123,8 +11195,8 @@
       <c r="A24" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="351"/>
-      <c r="C24" s="353"/>
+      <c r="B24" s="332"/>
+      <c r="C24" s="334"/>
       <c r="D24" s="122">
         <v>300</v>
       </c>
@@ -11168,8 +11240,8 @@
       <c r="A25" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="351"/>
-      <c r="C25" s="353"/>
+      <c r="B25" s="332"/>
+      <c r="C25" s="334"/>
       <c r="D25" s="122">
         <v>400</v>
       </c>
@@ -11213,8 +11285,8 @@
       <c r="A26" s="97" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="351"/>
-      <c r="C26" s="353"/>
+      <c r="B26" s="332"/>
+      <c r="C26" s="334"/>
       <c r="D26" s="122">
         <v>500</v>
       </c>
@@ -11254,7 +11326,7 @@
         <v>vendor3</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" ht="26">
       <c r="A27" s="97" t="s">
         <v>146</v>
       </c>
@@ -11338,7 +11410,7 @@
         <v>vendor9</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" ht="26">
       <c r="E29" s="109"/>
       <c r="H29" s="132"/>
       <c r="S29" s="133">
@@ -12312,17 +12384,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="U4:AV4"/>
     <mergeCell ref="B22:B26"/>
     <mergeCell ref="C22:C26"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="C12:C16"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="U4:AV4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12336,38 +12408,38 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2990"/>
-  <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="35.450000000000003"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="137"/>
-    <col min="2" max="2" width="10.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="83.7109375" style="137" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" style="137" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="137" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="137" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="137"/>
+    <col min="2" max="2" width="10.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.6640625" style="137" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" style="137" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="137" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="137" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="137" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" style="137" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="137" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="137" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" style="137" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" style="137" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" style="137" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="137" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" style="137" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="137" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="137" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21" style="179" customWidth="1"/>
-    <col min="18" max="18" width="65.140625" style="137" customWidth="1"/>
-    <col min="19" max="19" width="205.85546875" style="137" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.140625" style="137" bestFit="1" customWidth="1"/>
-    <col min="23" max="29" width="9.85546875" style="137" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.85546875" style="137"/>
+    <col min="18" max="18" width="65.1640625" style="137" customWidth="1"/>
+    <col min="19" max="19" width="205.83203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.1640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="9.83203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.83203125" style="137"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:20" s="269" customFormat="1" ht="40.5" customHeight="1">
-      <c r="B1" s="366" t="s">
+      <c r="B1" s="351" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="366"/>
-      <c r="D1" s="366"/>
+      <c r="C1" s="351"/>
+      <c r="D1" s="351"/>
       <c r="E1" s="270"/>
       <c r="H1" s="270"/>
       <c r="Q1" s="274"/>
@@ -12378,7 +12450,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="2:20" ht="204.6" customHeight="1">
+    <row r="2" spans="2:20" ht="204.5" customHeight="1">
       <c r="B2" s="175" t="s">
         <v>171</v>
       </c>
@@ -12432,10 +12504,10 @@
       </c>
     </row>
     <row r="3" spans="2:20">
-      <c r="B3" s="379">
+      <c r="B3" s="340">
         <v>1</v>
       </c>
-      <c r="C3" s="369" t="s">
+      <c r="C3" s="341" t="s">
         <v>175</v>
       </c>
       <c r="D3" s="140" t="s">
@@ -12478,9 +12550,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="2:20">
-      <c r="B4" s="379"/>
-      <c r="C4" s="369"/>
+    <row r="4" spans="2:20" ht="26">
+      <c r="B4" s="340"/>
+      <c r="C4" s="341"/>
       <c r="D4" s="142" t="s">
         <v>178</v>
       </c>
@@ -12522,10 +12594,10 @@
       </c>
     </row>
     <row r="5" spans="2:20">
-      <c r="B5" s="379">
+      <c r="B5" s="340">
         <v>2</v>
       </c>
-      <c r="C5" s="369" t="s">
+      <c r="C5" s="341" t="s">
         <v>179</v>
       </c>
       <c r="D5" s="140" t="s">
@@ -12568,9 +12640,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="2:20">
-      <c r="B6" s="383"/>
-      <c r="C6" s="369"/>
+    <row r="6" spans="2:20" ht="26">
+      <c r="B6" s="342"/>
+      <c r="C6" s="341"/>
       <c r="D6" s="142" t="s">
         <v>178</v>
       </c>
@@ -12615,7 +12687,7 @@
       <c r="B7" s="144">
         <v>3</v>
       </c>
-      <c r="C7" s="372" t="s">
+      <c r="C7" s="339" t="s">
         <v>180</v>
       </c>
       <c r="D7" s="140" t="s">
@@ -12658,9 +12730,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="2:20">
+    <row r="8" spans="2:20" ht="26">
       <c r="B8" s="77"/>
-      <c r="C8" s="372"/>
+      <c r="C8" s="339"/>
       <c r="D8" s="142" t="s">
         <v>178</v>
       </c>
@@ -12707,7 +12779,7 @@
       <c r="B9" s="144">
         <v>4</v>
       </c>
-      <c r="C9" s="372" t="s">
+      <c r="C9" s="339" t="s">
         <v>181</v>
       </c>
       <c r="D9" s="140" t="s">
@@ -12750,9 +12822,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="2:20">
+    <row r="10" spans="2:20" ht="26">
       <c r="B10" s="146"/>
-      <c r="C10" s="372"/>
+      <c r="C10" s="339"/>
       <c r="D10" s="142" t="s">
         <v>178</v>
       </c>
@@ -12796,10 +12868,10 @@
       </c>
     </row>
     <row r="11" spans="2:20">
-      <c r="B11" s="384">
+      <c r="B11" s="343">
         <v>5</v>
       </c>
-      <c r="C11" s="369" t="s">
+      <c r="C11" s="341" t="s">
         <v>182</v>
       </c>
       <c r="D11" s="140" t="s">
@@ -12842,9 +12914,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="2:20">
-      <c r="B12" s="379"/>
-      <c r="C12" s="369"/>
+    <row r="12" spans="2:20" ht="26">
+      <c r="B12" s="340"/>
+      <c r="C12" s="341"/>
       <c r="D12" s="142" t="s">
         <v>178</v>
       </c>
@@ -12888,10 +12960,10 @@
       </c>
     </row>
     <row r="13" spans="2:20">
-      <c r="B13" s="379">
+      <c r="B13" s="340">
         <v>6</v>
       </c>
-      <c r="C13" s="369" t="s">
+      <c r="C13" s="341" t="s">
         <v>183</v>
       </c>
       <c r="D13" s="140" t="s">
@@ -12934,9 +13006,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="2:20">
-      <c r="B14" s="383"/>
-      <c r="C14" s="369"/>
+    <row r="14" spans="2:20" ht="26">
+      <c r="B14" s="342"/>
+      <c r="C14" s="341"/>
       <c r="D14" s="142" t="s">
         <v>178</v>
       </c>
@@ -12981,7 +13053,7 @@
       <c r="B15" s="144">
         <v>7</v>
       </c>
-      <c r="C15" s="372" t="s">
+      <c r="C15" s="339" t="s">
         <v>184</v>
       </c>
       <c r="D15" s="140" t="s">
@@ -13024,9 +13096,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="2:20">
+    <row r="16" spans="2:20" ht="26">
       <c r="B16" s="77"/>
-      <c r="C16" s="372"/>
+      <c r="C16" s="339"/>
       <c r="D16" s="142" t="s">
         <v>178</v>
       </c>
@@ -13071,7 +13143,7 @@
       <c r="B17" s="144">
         <v>8</v>
       </c>
-      <c r="C17" s="372" t="s">
+      <c r="C17" s="339" t="s">
         <v>185</v>
       </c>
       <c r="D17" s="140" t="s">
@@ -13114,9 +13186,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="2:19">
+    <row r="18" spans="2:19" ht="26">
       <c r="B18" s="77"/>
-      <c r="C18" s="372"/>
+      <c r="C18" s="339"/>
       <c r="D18" s="142" t="s">
         <v>178</v>
       </c>
@@ -13161,7 +13233,7 @@
       <c r="B19" s="144">
         <v>9</v>
       </c>
-      <c r="C19" s="372" t="s">
+      <c r="C19" s="339" t="s">
         <v>186</v>
       </c>
       <c r="D19" s="140" t="s">
@@ -13204,9 +13276,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="2:19">
+    <row r="20" spans="2:19" ht="26">
       <c r="B20" s="77"/>
-      <c r="C20" s="372"/>
+      <c r="C20" s="339"/>
       <c r="D20" s="142" t="s">
         <v>178</v>
       </c>
@@ -13248,10 +13320,10 @@
       </c>
     </row>
     <row r="21" spans="2:19">
-      <c r="B21" s="368">
+      <c r="B21" s="346">
         <v>10</v>
       </c>
-      <c r="C21" s="376" t="s">
+      <c r="C21" s="348" t="s">
         <v>188</v>
       </c>
       <c r="D21" s="140" t="s">
@@ -13302,8 +13374,8 @@
       </c>
     </row>
     <row r="22" spans="2:19">
-      <c r="B22" s="373"/>
-      <c r="C22" s="376"/>
+      <c r="B22" s="347"/>
+      <c r="C22" s="348"/>
       <c r="D22" s="140" t="s">
         <v>190</v>
       </c>
@@ -13352,8 +13424,8 @@
       </c>
     </row>
     <row r="23" spans="2:19">
-      <c r="B23" s="373"/>
-      <c r="C23" s="376"/>
+      <c r="B23" s="347"/>
+      <c r="C23" s="348"/>
       <c r="D23" s="149" t="s">
         <v>191</v>
       </c>
@@ -13403,7 +13475,7 @@
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="148"/>
-      <c r="C24" s="376"/>
+      <c r="C24" s="348"/>
       <c r="D24" s="149" t="s">
         <v>89</v>
       </c>
@@ -13453,7 +13525,7 @@
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="148"/>
-      <c r="C25" s="376"/>
+      <c r="C25" s="348"/>
       <c r="D25" s="149" t="s">
         <v>192</v>
       </c>
@@ -13503,7 +13575,7 @@
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="148"/>
-      <c r="C26" s="377"/>
+      <c r="C26" s="349"/>
       <c r="D26" s="149" t="s">
         <v>193</v>
       </c>
@@ -13555,7 +13627,7 @@
       <c r="B27" s="150">
         <v>11</v>
       </c>
-      <c r="C27" s="380" t="s">
+      <c r="C27" s="344" t="s">
         <v>194</v>
       </c>
       <c r="D27" s="140" t="s">
@@ -13605,7 +13677,7 @@
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="152"/>
-      <c r="C28" s="381"/>
+      <c r="C28" s="345"/>
       <c r="D28" s="140" t="s">
         <v>190</v>
       </c>
@@ -13655,7 +13727,7 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="152"/>
-      <c r="C29" s="381"/>
+      <c r="C29" s="345"/>
       <c r="D29" s="149" t="s">
         <v>191</v>
       </c>
@@ -13705,7 +13777,7 @@
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="152"/>
-      <c r="C30" s="381"/>
+      <c r="C30" s="345"/>
       <c r="D30" s="149" t="s">
         <v>89</v>
       </c>
@@ -13755,7 +13827,7 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="152"/>
-      <c r="C31" s="381"/>
+      <c r="C31" s="345"/>
       <c r="D31" s="149" t="s">
         <v>192</v>
       </c>
@@ -13856,10 +13928,10 @@
       </c>
     </row>
     <row r="33" spans="2:19">
-      <c r="B33" s="368">
+      <c r="B33" s="346">
         <v>12</v>
       </c>
-      <c r="C33" s="382" t="s">
+      <c r="C33" s="350" t="s">
         <v>195</v>
       </c>
       <c r="D33" s="140" t="s">
@@ -13910,8 +13982,8 @@
       </c>
     </row>
     <row r="34" spans="2:19">
-      <c r="B34" s="373"/>
-      <c r="C34" s="376"/>
+      <c r="B34" s="347"/>
+      <c r="C34" s="348"/>
       <c r="D34" s="140" t="s">
         <v>190</v>
       </c>
@@ -13960,8 +14032,8 @@
       </c>
     </row>
     <row r="35" spans="2:19">
-      <c r="B35" s="373"/>
-      <c r="C35" s="376"/>
+      <c r="B35" s="347"/>
+      <c r="C35" s="348"/>
       <c r="D35" s="149" t="s">
         <v>191</v>
       </c>
@@ -14011,7 +14083,7 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="148"/>
-      <c r="C36" s="376"/>
+      <c r="C36" s="348"/>
       <c r="D36" s="149" t="s">
         <v>89</v>
       </c>
@@ -14061,7 +14133,7 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="148"/>
-      <c r="C37" s="376"/>
+      <c r="C37" s="348"/>
       <c r="D37" s="149" t="s">
         <v>192</v>
       </c>
@@ -14111,7 +14183,7 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="148"/>
-      <c r="C38" s="376"/>
+      <c r="C38" s="348"/>
       <c r="D38" s="149" t="s">
         <v>193</v>
       </c>
@@ -14162,10 +14234,10 @@
       </c>
     </row>
     <row r="39" spans="2:19">
-      <c r="B39" s="368">
+      <c r="B39" s="346">
         <v>13</v>
       </c>
-      <c r="C39" s="376" t="s">
+      <c r="C39" s="348" t="s">
         <v>196</v>
       </c>
       <c r="D39" s="140" t="s">
@@ -14216,8 +14288,8 @@
       </c>
     </row>
     <row r="40" spans="2:19">
-      <c r="B40" s="373"/>
-      <c r="C40" s="376"/>
+      <c r="B40" s="347"/>
+      <c r="C40" s="348"/>
       <c r="D40" s="140" t="s">
         <v>190</v>
       </c>
@@ -14266,8 +14338,8 @@
       </c>
     </row>
     <row r="41" spans="2:19">
-      <c r="B41" s="373"/>
-      <c r="C41" s="376"/>
+      <c r="B41" s="347"/>
+      <c r="C41" s="348"/>
       <c r="D41" s="149" t="s">
         <v>191</v>
       </c>
@@ -14317,7 +14389,7 @@
     </row>
     <row r="42" spans="2:19">
       <c r="B42" s="148"/>
-      <c r="C42" s="376"/>
+      <c r="C42" s="348"/>
       <c r="D42" s="149" t="s">
         <v>89</v>
       </c>
@@ -14367,7 +14439,7 @@
     </row>
     <row r="43" spans="2:19">
       <c r="B43" s="148"/>
-      <c r="C43" s="376"/>
+      <c r="C43" s="348"/>
       <c r="D43" s="149" t="s">
         <v>192</v>
       </c>
@@ -14417,7 +14489,7 @@
     </row>
     <row r="44" spans="2:19">
       <c r="B44" s="148"/>
-      <c r="C44" s="377"/>
+      <c r="C44" s="349"/>
       <c r="D44" s="149" t="s">
         <v>193</v>
       </c>
@@ -14469,7 +14541,7 @@
       <c r="B45" s="150">
         <v>14</v>
       </c>
-      <c r="C45" s="380" t="s">
+      <c r="C45" s="344" t="s">
         <v>197</v>
       </c>
       <c r="D45" s="140" t="s">
@@ -14521,7 +14593,7 @@
     </row>
     <row r="46" spans="2:19">
       <c r="B46" s="152"/>
-      <c r="C46" s="381"/>
+      <c r="C46" s="345"/>
       <c r="D46" s="140" t="s">
         <v>190</v>
       </c>
@@ -14571,7 +14643,7 @@
     </row>
     <row r="47" spans="2:19">
       <c r="B47" s="152"/>
-      <c r="C47" s="381"/>
+      <c r="C47" s="345"/>
       <c r="D47" s="149" t="s">
         <v>191</v>
       </c>
@@ -14621,7 +14693,7 @@
     </row>
     <row r="48" spans="2:19">
       <c r="B48" s="152"/>
-      <c r="C48" s="381"/>
+      <c r="C48" s="345"/>
       <c r="D48" s="149" t="s">
         <v>89</v>
       </c>
@@ -14671,7 +14743,7 @@
     </row>
     <row r="49" spans="2:19">
       <c r="B49" s="152"/>
-      <c r="C49" s="381"/>
+      <c r="C49" s="345"/>
       <c r="D49" s="149" t="s">
         <v>192</v>
       </c>
@@ -14770,10 +14842,10 @@
       </c>
     </row>
     <row r="51" spans="2:19">
-      <c r="B51" s="368">
+      <c r="B51" s="346">
         <v>15</v>
       </c>
-      <c r="C51" s="382" t="s">
+      <c r="C51" s="350" t="s">
         <v>198</v>
       </c>
       <c r="D51" s="140" t="s">
@@ -14824,8 +14896,8 @@
       </c>
     </row>
     <row r="52" spans="2:19">
-      <c r="B52" s="373"/>
-      <c r="C52" s="376"/>
+      <c r="B52" s="347"/>
+      <c r="C52" s="348"/>
       <c r="D52" s="140" t="s">
         <v>190</v>
       </c>
@@ -14874,8 +14946,8 @@
       </c>
     </row>
     <row r="53" spans="2:19">
-      <c r="B53" s="373"/>
-      <c r="C53" s="376"/>
+      <c r="B53" s="347"/>
+      <c r="C53" s="348"/>
       <c r="D53" s="149" t="s">
         <v>191</v>
       </c>
@@ -14925,7 +14997,7 @@
     </row>
     <row r="54" spans="2:19">
       <c r="B54" s="148"/>
-      <c r="C54" s="376"/>
+      <c r="C54" s="348"/>
       <c r="D54" s="149" t="s">
         <v>89</v>
       </c>
@@ -14977,7 +15049,7 @@
     </row>
     <row r="55" spans="2:19">
       <c r="B55" s="148"/>
-      <c r="C55" s="376"/>
+      <c r="C55" s="348"/>
       <c r="D55" s="149" t="s">
         <v>192</v>
       </c>
@@ -15027,7 +15099,7 @@
     </row>
     <row r="56" spans="2:19">
       <c r="B56" s="148"/>
-      <c r="C56" s="377"/>
+      <c r="C56" s="349"/>
       <c r="D56" s="149" t="s">
         <v>193</v>
       </c>
@@ -15079,7 +15151,7 @@
       <c r="B57" s="150">
         <v>16</v>
       </c>
-      <c r="C57" s="380" t="s">
+      <c r="C57" s="344" t="s">
         <v>199</v>
       </c>
       <c r="D57" s="140" t="s">
@@ -15131,7 +15203,7 @@
     </row>
     <row r="58" spans="2:19">
       <c r="B58" s="152"/>
-      <c r="C58" s="381"/>
+      <c r="C58" s="345"/>
       <c r="D58" s="140" t="s">
         <v>190</v>
       </c>
@@ -15181,7 +15253,7 @@
     </row>
     <row r="59" spans="2:19">
       <c r="B59" s="152"/>
-      <c r="C59" s="381"/>
+      <c r="C59" s="345"/>
       <c r="D59" s="149" t="s">
         <v>191</v>
       </c>
@@ -15231,7 +15303,7 @@
     </row>
     <row r="60" spans="2:19">
       <c r="B60" s="152"/>
-      <c r="C60" s="381"/>
+      <c r="C60" s="345"/>
       <c r="D60" s="149" t="s">
         <v>89</v>
       </c>
@@ -15283,7 +15355,7 @@
     </row>
     <row r="61" spans="2:19">
       <c r="B61" s="152"/>
-      <c r="C61" s="381"/>
+      <c r="C61" s="345"/>
       <c r="D61" s="149" t="s">
         <v>192</v>
       </c>
@@ -15382,10 +15454,10 @@
       </c>
     </row>
     <row r="63" spans="2:19">
-      <c r="B63" s="368">
+      <c r="B63" s="346">
         <v>17</v>
       </c>
-      <c r="C63" s="382" t="s">
+      <c r="C63" s="350" t="s">
         <v>200</v>
       </c>
       <c r="D63" s="140" t="s">
@@ -15434,8 +15506,8 @@
       </c>
     </row>
     <row r="64" spans="2:19">
-      <c r="B64" s="373"/>
-      <c r="C64" s="376"/>
+      <c r="B64" s="347"/>
+      <c r="C64" s="348"/>
       <c r="D64" s="140" t="s">
         <v>190</v>
       </c>
@@ -15482,8 +15554,8 @@
       </c>
     </row>
     <row r="65" spans="2:19">
-      <c r="B65" s="373"/>
-      <c r="C65" s="376"/>
+      <c r="B65" s="347"/>
+      <c r="C65" s="348"/>
       <c r="D65" s="149" t="s">
         <v>191</v>
       </c>
@@ -15531,7 +15603,7 @@
     </row>
     <row r="66" spans="2:19">
       <c r="B66" s="148"/>
-      <c r="C66" s="376"/>
+      <c r="C66" s="348"/>
       <c r="D66" s="149" t="s">
         <v>89</v>
       </c>
@@ -15579,7 +15651,7 @@
     </row>
     <row r="67" spans="2:19">
       <c r="B67" s="148"/>
-      <c r="C67" s="376"/>
+      <c r="C67" s="348"/>
       <c r="D67" s="149" t="s">
         <v>192</v>
       </c>
@@ -15627,7 +15699,7 @@
     </row>
     <row r="68" spans="2:19">
       <c r="B68" s="148"/>
-      <c r="C68" s="377"/>
+      <c r="C68" s="349"/>
       <c r="D68" s="149" t="s">
         <v>193</v>
       </c>
@@ -15677,7 +15749,7 @@
       <c r="B69" s="150">
         <v>18</v>
       </c>
-      <c r="C69" s="380" t="s">
+      <c r="C69" s="344" t="s">
         <v>201</v>
       </c>
       <c r="D69" s="140" t="s">
@@ -15727,7 +15799,7 @@
     </row>
     <row r="70" spans="2:19">
       <c r="B70" s="152"/>
-      <c r="C70" s="381"/>
+      <c r="C70" s="345"/>
       <c r="D70" s="140" t="s">
         <v>190</v>
       </c>
@@ -15775,7 +15847,7 @@
     </row>
     <row r="71" spans="2:19">
       <c r="B71" s="152"/>
-      <c r="C71" s="381"/>
+      <c r="C71" s="345"/>
       <c r="D71" s="149" t="s">
         <v>191</v>
       </c>
@@ -15823,7 +15895,7 @@
     </row>
     <row r="72" spans="2:19">
       <c r="B72" s="152"/>
-      <c r="C72" s="381"/>
+      <c r="C72" s="345"/>
       <c r="D72" s="149" t="s">
         <v>89</v>
       </c>
@@ -15871,7 +15943,7 @@
     </row>
     <row r="73" spans="2:19">
       <c r="B73" s="152"/>
-      <c r="C73" s="381"/>
+      <c r="C73" s="345"/>
       <c r="D73" s="149" t="s">
         <v>192</v>
       </c>
@@ -15966,10 +16038,10 @@
       </c>
     </row>
     <row r="75" spans="2:19">
-      <c r="B75" s="368">
+      <c r="B75" s="346">
         <v>19</v>
       </c>
-      <c r="C75" s="382" t="s">
+      <c r="C75" s="350" t="s">
         <v>202</v>
       </c>
       <c r="D75" s="140" t="s">
@@ -16018,8 +16090,8 @@
       </c>
     </row>
     <row r="76" spans="2:19">
-      <c r="B76" s="373"/>
-      <c r="C76" s="376"/>
+      <c r="B76" s="347"/>
+      <c r="C76" s="348"/>
       <c r="D76" s="140" t="s">
         <v>190</v>
       </c>
@@ -16066,8 +16138,8 @@
       </c>
     </row>
     <row r="77" spans="2:19">
-      <c r="B77" s="373"/>
-      <c r="C77" s="376"/>
+      <c r="B77" s="347"/>
+      <c r="C77" s="348"/>
       <c r="D77" s="149" t="s">
         <v>191</v>
       </c>
@@ -16115,7 +16187,7 @@
     </row>
     <row r="78" spans="2:19">
       <c r="B78" s="148"/>
-      <c r="C78" s="376"/>
+      <c r="C78" s="348"/>
       <c r="D78" s="149" t="s">
         <v>89</v>
       </c>
@@ -16163,7 +16235,7 @@
     </row>
     <row r="79" spans="2:19">
       <c r="B79" s="148"/>
-      <c r="C79" s="376"/>
+      <c r="C79" s="348"/>
       <c r="D79" s="149" t="s">
         <v>192</v>
       </c>
@@ -16211,7 +16283,7 @@
     </row>
     <row r="80" spans="2:19">
       <c r="B80" s="148"/>
-      <c r="C80" s="377"/>
+      <c r="C80" s="349"/>
       <c r="D80" s="149" t="s">
         <v>193</v>
       </c>
@@ -16261,7 +16333,7 @@
       <c r="B81" s="150">
         <v>20</v>
       </c>
-      <c r="C81" s="380" t="s">
+      <c r="C81" s="344" t="s">
         <v>203</v>
       </c>
       <c r="D81" s="140" t="s">
@@ -16311,7 +16383,7 @@
     </row>
     <row r="82" spans="2:19">
       <c r="B82" s="152"/>
-      <c r="C82" s="381"/>
+      <c r="C82" s="345"/>
       <c r="D82" s="140" t="s">
         <v>190</v>
       </c>
@@ -16359,7 +16431,7 @@
     </row>
     <row r="83" spans="2:19">
       <c r="B83" s="152"/>
-      <c r="C83" s="381"/>
+      <c r="C83" s="345"/>
       <c r="D83" s="149" t="s">
         <v>191</v>
       </c>
@@ -16407,7 +16479,7 @@
     </row>
     <row r="84" spans="2:19">
       <c r="B84" s="152"/>
-      <c r="C84" s="381"/>
+      <c r="C84" s="345"/>
       <c r="D84" s="149" t="s">
         <v>89</v>
       </c>
@@ -16457,7 +16529,7 @@
     </row>
     <row r="85" spans="2:19">
       <c r="B85" s="152"/>
-      <c r="C85" s="381"/>
+      <c r="C85" s="345"/>
       <c r="D85" s="149" t="s">
         <v>192</v>
       </c>
@@ -16552,10 +16624,10 @@
       </c>
     </row>
     <row r="87" spans="2:19">
-      <c r="B87" s="368">
+      <c r="B87" s="346">
         <v>21</v>
       </c>
-      <c r="C87" s="382" t="s">
+      <c r="C87" s="350" t="s">
         <v>204</v>
       </c>
       <c r="D87" s="140" t="s">
@@ -16606,8 +16678,8 @@
       </c>
     </row>
     <row r="88" spans="2:19">
-      <c r="B88" s="373"/>
-      <c r="C88" s="376"/>
+      <c r="B88" s="347"/>
+      <c r="C88" s="348"/>
       <c r="D88" s="140" t="s">
         <v>190</v>
       </c>
@@ -16656,8 +16728,8 @@
       </c>
     </row>
     <row r="89" spans="2:19">
-      <c r="B89" s="373"/>
-      <c r="C89" s="376"/>
+      <c r="B89" s="347"/>
+      <c r="C89" s="348"/>
       <c r="D89" s="149" t="s">
         <v>191</v>
       </c>
@@ -16707,7 +16779,7 @@
     </row>
     <row r="90" spans="2:19">
       <c r="B90" s="148"/>
-      <c r="C90" s="376"/>
+      <c r="C90" s="348"/>
       <c r="D90" s="149" t="s">
         <v>89</v>
       </c>
@@ -16757,7 +16829,7 @@
     </row>
     <row r="91" spans="2:19">
       <c r="B91" s="148"/>
-      <c r="C91" s="376"/>
+      <c r="C91" s="348"/>
       <c r="D91" s="149" t="s">
         <v>192</v>
       </c>
@@ -16807,7 +16879,7 @@
     </row>
     <row r="92" spans="2:19">
       <c r="B92" s="148"/>
-      <c r="C92" s="377"/>
+      <c r="C92" s="349"/>
       <c r="D92" s="149" t="s">
         <v>193</v>
       </c>
@@ -16859,7 +16931,7 @@
       <c r="B93" s="150">
         <v>22</v>
       </c>
-      <c r="C93" s="380" t="s">
+      <c r="C93" s="344" t="s">
         <v>205</v>
       </c>
       <c r="D93" s="140" t="s">
@@ -16911,7 +16983,7 @@
     </row>
     <row r="94" spans="2:19">
       <c r="B94" s="152"/>
-      <c r="C94" s="381"/>
+      <c r="C94" s="345"/>
       <c r="D94" s="140" t="s">
         <v>190</v>
       </c>
@@ -16961,7 +17033,7 @@
     </row>
     <row r="95" spans="2:19">
       <c r="B95" s="152"/>
-      <c r="C95" s="381"/>
+      <c r="C95" s="345"/>
       <c r="D95" s="149" t="s">
         <v>191</v>
       </c>
@@ -17011,7 +17083,7 @@
     </row>
     <row r="96" spans="2:19">
       <c r="B96" s="152"/>
-      <c r="C96" s="381"/>
+      <c r="C96" s="345"/>
       <c r="D96" s="149" t="s">
         <v>89</v>
       </c>
@@ -17063,7 +17135,7 @@
     </row>
     <row r="97" spans="2:19">
       <c r="B97" s="152"/>
-      <c r="C97" s="381"/>
+      <c r="C97" s="345"/>
       <c r="D97" s="149" t="s">
         <v>192</v>
       </c>
@@ -17165,7 +17237,7 @@
       <c r="B99" s="150">
         <v>23</v>
       </c>
-      <c r="C99" s="380" t="s">
+      <c r="C99" s="344" t="s">
         <v>206</v>
       </c>
       <c r="D99" s="140" t="s">
@@ -17215,7 +17287,7 @@
     </row>
     <row r="100" spans="2:19">
       <c r="B100" s="152"/>
-      <c r="C100" s="381"/>
+      <c r="C100" s="345"/>
       <c r="D100" s="140" t="s">
         <v>190</v>
       </c>
@@ -17263,7 +17335,7 @@
     </row>
     <row r="101" spans="2:19">
       <c r="B101" s="152"/>
-      <c r="C101" s="381"/>
+      <c r="C101" s="345"/>
       <c r="D101" s="149" t="s">
         <v>191</v>
       </c>
@@ -17311,7 +17383,7 @@
     </row>
     <row r="102" spans="2:19">
       <c r="B102" s="152"/>
-      <c r="C102" s="381"/>
+      <c r="C102" s="345"/>
       <c r="D102" s="149" t="s">
         <v>89</v>
       </c>
@@ -17359,7 +17431,7 @@
     </row>
     <row r="103" spans="2:19">
       <c r="B103" s="152"/>
-      <c r="C103" s="381"/>
+      <c r="C103" s="345"/>
       <c r="D103" s="149" t="s">
         <v>192</v>
       </c>
@@ -17457,7 +17529,7 @@
       <c r="B105" s="150">
         <v>24</v>
       </c>
-      <c r="C105" s="380" t="s">
+      <c r="C105" s="344" t="s">
         <v>207</v>
       </c>
       <c r="D105" s="140" t="s">
@@ -17505,7 +17577,7 @@
     </row>
     <row r="106" spans="2:19">
       <c r="B106" s="152"/>
-      <c r="C106" s="381"/>
+      <c r="C106" s="345"/>
       <c r="D106" s="140" t="s">
         <v>190</v>
       </c>
@@ -17551,7 +17623,7 @@
     </row>
     <row r="107" spans="2:19">
       <c r="B107" s="152"/>
-      <c r="C107" s="381"/>
+      <c r="C107" s="345"/>
       <c r="D107" s="149" t="s">
         <v>191</v>
       </c>
@@ -17597,7 +17669,7 @@
     </row>
     <row r="108" spans="2:19">
       <c r="B108" s="152"/>
-      <c r="C108" s="381"/>
+      <c r="C108" s="345"/>
       <c r="D108" s="149" t="s">
         <v>89</v>
       </c>
@@ -17643,7 +17715,7 @@
     </row>
     <row r="109" spans="2:19">
       <c r="B109" s="152"/>
-      <c r="C109" s="381"/>
+      <c r="C109" s="345"/>
       <c r="D109" s="149" t="s">
         <v>192</v>
       </c>
@@ -17775,7 +17847,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="112" spans="2:19" ht="32.450000000000003" customHeight="1">
+    <row r="112" spans="2:19" ht="32.5" customHeight="1">
       <c r="B112" s="152"/>
       <c r="C112" s="153" t="s">
         <v>210</v>
@@ -17815,7 +17887,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="113" spans="2:19">
+    <row r="113" spans="2:19" ht="26">
       <c r="B113" s="150">
         <v>26</v>
       </c>
@@ -17857,7 +17929,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="2:19" ht="41.45" customHeight="1">
+    <row r="114" spans="2:19" ht="41.5" customHeight="1">
       <c r="B114" s="152"/>
       <c r="C114" s="153" t="s">
         <v>213</v>
@@ -17897,7 +17969,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="2:19">
+    <row r="115" spans="2:19" ht="26">
       <c r="B115" s="150">
         <v>27</v>
       </c>
@@ -17990,7 +18062,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="117" spans="2:19" ht="36.950000000000003" customHeight="1">
+    <row r="117" spans="2:19" ht="37" customHeight="1">
       <c r="B117" s="150">
         <v>28</v>
       </c>
@@ -18034,7 +18106,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="118" spans="2:19">
+    <row r="118" spans="2:19" ht="26">
       <c r="B118" s="152"/>
       <c r="C118" s="153" t="s">
         <v>219</v>
@@ -18078,7 +18150,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="119" spans="2:19" ht="33.6" customHeight="1">
+    <row r="119" spans="2:19" ht="33.5" customHeight="1">
       <c r="B119" s="150">
         <v>29</v>
       </c>
@@ -18124,7 +18196,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="120" spans="2:19">
+    <row r="120" spans="2:19" ht="26">
       <c r="B120" s="152"/>
       <c r="C120" s="153" t="s">
         <v>219</v>
@@ -18168,7 +18240,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="121" spans="2:19">
+    <row r="121" spans="2:19" ht="26">
       <c r="B121" s="150">
         <v>30</v>
       </c>
@@ -18214,7 +18286,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="122" spans="2:19" ht="30.95" customHeight="1">
+    <row r="122" spans="2:19" ht="31" customHeight="1">
       <c r="B122" s="152"/>
       <c r="C122" s="153" t="s">
         <v>224</v>
@@ -18260,7 +18332,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="123" spans="2:19">
+    <row r="123" spans="2:19" ht="26">
       <c r="B123" s="150">
         <v>31</v>
       </c>
@@ -18362,7 +18434,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="125" spans="2:19">
+    <row r="125" spans="2:19" ht="26">
       <c r="B125" s="152"/>
       <c r="C125" s="164" t="s">
         <v>227</v>
@@ -18412,7 +18484,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="126" spans="2:19">
+    <row r="126" spans="2:19" ht="26">
       <c r="B126" s="152"/>
       <c r="C126" s="165" t="s">
         <v>228</v>
@@ -18466,7 +18538,7 @@
       <c r="B127" s="144">
         <v>32</v>
       </c>
-      <c r="C127" s="371" t="s">
+      <c r="C127" s="356" t="s">
         <v>229</v>
       </c>
       <c r="D127" s="149">
@@ -18516,7 +18588,7 @@
     </row>
     <row r="128" spans="2:19">
       <c r="B128" s="148"/>
-      <c r="C128" s="372"/>
+      <c r="C128" s="339"/>
       <c r="D128" s="149">
         <v>500</v>
       </c>
@@ -18564,7 +18636,7 @@
     </row>
     <row r="129" spans="2:19">
       <c r="B129" s="148"/>
-      <c r="C129" s="372"/>
+      <c r="C129" s="339"/>
       <c r="D129" s="149">
         <v>1000</v>
       </c>
@@ -18612,7 +18684,7 @@
     </row>
     <row r="130" spans="2:19">
       <c r="B130" s="148"/>
-      <c r="C130" s="372"/>
+      <c r="C130" s="339"/>
       <c r="D130" s="149">
         <v>5000</v>
       </c>
@@ -18662,7 +18734,7 @@
       <c r="B131" s="143">
         <v>33</v>
       </c>
-      <c r="C131" s="376" t="s">
+      <c r="C131" s="348" t="s">
         <v>230</v>
       </c>
       <c r="D131" s="149">
@@ -18712,7 +18784,7 @@
     </row>
     <row r="132" spans="2:19">
       <c r="B132" s="148"/>
-      <c r="C132" s="376"/>
+      <c r="C132" s="348"/>
       <c r="D132" s="149">
         <v>500</v>
       </c>
@@ -18760,7 +18832,7 @@
     </row>
     <row r="133" spans="2:19">
       <c r="B133" s="148"/>
-      <c r="C133" s="376"/>
+      <c r="C133" s="348"/>
       <c r="D133" s="149">
         <v>1000</v>
       </c>
@@ -18808,7 +18880,7 @@
     </row>
     <row r="134" spans="2:19">
       <c r="B134" s="148"/>
-      <c r="C134" s="377"/>
+      <c r="C134" s="349"/>
       <c r="D134" s="149">
         <v>5000</v>
       </c>
@@ -18858,7 +18930,7 @@
       <c r="B135" s="166">
         <v>34</v>
       </c>
-      <c r="C135" s="370" t="s">
+      <c r="C135" s="355" t="s">
         <v>231</v>
       </c>
       <c r="D135" s="140" t="s">
@@ -18908,7 +18980,7 @@
     </row>
     <row r="136" spans="2:19">
       <c r="B136" s="152"/>
-      <c r="C136" s="378"/>
+      <c r="C136" s="359"/>
       <c r="D136" s="140" t="s">
         <v>233</v>
       </c>
@@ -18954,7 +19026,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="137" spans="2:19">
+    <row r="137" spans="2:19" ht="26">
       <c r="B137" s="152"/>
       <c r="C137" s="164" t="s">
         <v>228</v>
@@ -19004,7 +19076,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="138" spans="2:19">
+    <row r="138" spans="2:19" ht="26">
       <c r="B138" s="152"/>
       <c r="C138" s="167" t="s">
         <v>235</v>
@@ -19054,7 +19126,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="139" spans="2:19">
+    <row r="139" spans="2:19" ht="26">
       <c r="B139" s="152"/>
       <c r="C139" s="167" t="s">
         <v>237</v>
@@ -19105,10 +19177,10 @@
       </c>
     </row>
     <row r="140" spans="2:19">
-      <c r="B140" s="379">
+      <c r="B140" s="340">
         <v>35</v>
       </c>
-      <c r="C140" s="369" t="s">
+      <c r="C140" s="341" t="s">
         <v>239</v>
       </c>
       <c r="D140" s="140" t="s">
@@ -19157,8 +19229,8 @@
       </c>
     </row>
     <row r="141" spans="2:19">
-      <c r="B141" s="379"/>
-      <c r="C141" s="369"/>
+      <c r="B141" s="340"/>
+      <c r="C141" s="341"/>
       <c r="D141" s="140" t="s">
         <v>178</v>
       </c>
@@ -19205,8 +19277,8 @@
       </c>
     </row>
     <row r="142" spans="2:19">
-      <c r="B142" s="379"/>
-      <c r="C142" s="369"/>
+      <c r="B142" s="340"/>
+      <c r="C142" s="341"/>
       <c r="D142" s="140" t="s">
         <v>190</v>
       </c>
@@ -19253,8 +19325,8 @@
       </c>
     </row>
     <row r="143" spans="2:19">
-      <c r="B143" s="379"/>
-      <c r="C143" s="369"/>
+      <c r="B143" s="340"/>
+      <c r="C143" s="341"/>
       <c r="D143" s="140" t="s">
         <v>191</v>
       </c>
@@ -19301,8 +19373,8 @@
       </c>
     </row>
     <row r="144" spans="2:19">
-      <c r="B144" s="379"/>
-      <c r="C144" s="369"/>
+      <c r="B144" s="340"/>
+      <c r="C144" s="341"/>
       <c r="D144" s="140" t="s">
         <v>240</v>
       </c>
@@ -19351,8 +19423,8 @@
       </c>
     </row>
     <row r="145" spans="2:19">
-      <c r="B145" s="379"/>
-      <c r="C145" s="369"/>
+      <c r="B145" s="340"/>
+      <c r="C145" s="341"/>
       <c r="D145" s="140" t="s">
         <v>105</v>
       </c>
@@ -19401,8 +19473,8 @@
       </c>
     </row>
     <row r="146" spans="2:19">
-      <c r="B146" s="379"/>
-      <c r="C146" s="369"/>
+      <c r="B146" s="340"/>
+      <c r="C146" s="341"/>
       <c r="D146" s="140" t="s">
         <v>91</v>
       </c>
@@ -19451,10 +19523,10 @@
       </c>
     </row>
     <row r="147" spans="2:19">
-      <c r="B147" s="379">
+      <c r="B147" s="340">
         <v>36</v>
       </c>
-      <c r="C147" s="369" t="s">
+      <c r="C147" s="341" t="s">
         <v>241</v>
       </c>
       <c r="D147" s="140" t="s">
@@ -19501,8 +19573,8 @@
       </c>
     </row>
     <row r="148" spans="2:19">
-      <c r="B148" s="379"/>
-      <c r="C148" s="369"/>
+      <c r="B148" s="340"/>
+      <c r="C148" s="341"/>
       <c r="D148" s="140" t="s">
         <v>178</v>
       </c>
@@ -19549,8 +19621,8 @@
       </c>
     </row>
     <row r="149" spans="2:19">
-      <c r="B149" s="379"/>
-      <c r="C149" s="369"/>
+      <c r="B149" s="340"/>
+      <c r="C149" s="341"/>
       <c r="D149" s="140" t="s">
         <v>190</v>
       </c>
@@ -19597,8 +19669,8 @@
       </c>
     </row>
     <row r="150" spans="2:19">
-      <c r="B150" s="379"/>
-      <c r="C150" s="369"/>
+      <c r="B150" s="340"/>
+      <c r="C150" s="341"/>
       <c r="D150" s="140" t="s">
         <v>191</v>
       </c>
@@ -19645,8 +19717,8 @@
       </c>
     </row>
     <row r="151" spans="2:19">
-      <c r="B151" s="379"/>
-      <c r="C151" s="369"/>
+      <c r="B151" s="340"/>
+      <c r="C151" s="341"/>
       <c r="D151" s="140" t="s">
         <v>240</v>
       </c>
@@ -19695,8 +19767,8 @@
       </c>
     </row>
     <row r="152" spans="2:19">
-      <c r="B152" s="379"/>
-      <c r="C152" s="369"/>
+      <c r="B152" s="340"/>
+      <c r="C152" s="341"/>
       <c r="D152" s="140" t="s">
         <v>105</v>
       </c>
@@ -19745,8 +19817,8 @@
       </c>
     </row>
     <row r="153" spans="2:19">
-      <c r="B153" s="379"/>
-      <c r="C153" s="369"/>
+      <c r="B153" s="340"/>
+      <c r="C153" s="341"/>
       <c r="D153" s="140" t="s">
         <v>91</v>
       </c>
@@ -19795,10 +19867,10 @@
       </c>
     </row>
     <row r="154" spans="2:19">
-      <c r="B154" s="367">
+      <c r="B154" s="354">
         <v>37</v>
       </c>
-      <c r="C154" s="369" t="s">
+      <c r="C154" s="341" t="s">
         <v>242</v>
       </c>
       <c r="D154" s="140" t="s">
@@ -19847,8 +19919,8 @@
       </c>
     </row>
     <row r="155" spans="2:19">
-      <c r="B155" s="367"/>
-      <c r="C155" s="369"/>
+      <c r="B155" s="354"/>
+      <c r="C155" s="341"/>
       <c r="D155" s="140" t="s">
         <v>178</v>
       </c>
@@ -19895,8 +19967,8 @@
       </c>
     </row>
     <row r="156" spans="2:19">
-      <c r="B156" s="367"/>
-      <c r="C156" s="369"/>
+      <c r="B156" s="354"/>
+      <c r="C156" s="341"/>
       <c r="D156" s="140" t="s">
         <v>190</v>
       </c>
@@ -19943,8 +20015,8 @@
       </c>
     </row>
     <row r="157" spans="2:19">
-      <c r="B157" s="367"/>
-      <c r="C157" s="369"/>
+      <c r="B157" s="354"/>
+      <c r="C157" s="341"/>
       <c r="D157" s="140" t="s">
         <v>191</v>
       </c>
@@ -19991,8 +20063,8 @@
       </c>
     </row>
     <row r="158" spans="2:19">
-      <c r="B158" s="367"/>
-      <c r="C158" s="369"/>
+      <c r="B158" s="354"/>
+      <c r="C158" s="341"/>
       <c r="D158" s="140" t="s">
         <v>240</v>
       </c>
@@ -20041,8 +20113,8 @@
       </c>
     </row>
     <row r="159" spans="2:19">
-      <c r="B159" s="367"/>
-      <c r="C159" s="369"/>
+      <c r="B159" s="354"/>
+      <c r="C159" s="341"/>
       <c r="D159" s="140" t="s">
         <v>105</v>
       </c>
@@ -20091,8 +20163,8 @@
       </c>
     </row>
     <row r="160" spans="2:19">
-      <c r="B160" s="368"/>
-      <c r="C160" s="370"/>
+      <c r="B160" s="346"/>
+      <c r="C160" s="355"/>
       <c r="D160" s="140" t="s">
         <v>91</v>
       </c>
@@ -20140,7 +20212,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="161" spans="2:19">
+    <row r="161" spans="2:19" ht="26">
       <c r="B161" s="150">
         <v>38</v>
       </c>
@@ -20187,7 +20259,7 @@
         <v>vendor7</v>
       </c>
     </row>
-    <row r="162" spans="2:19">
+    <row r="162" spans="2:19" ht="26">
       <c r="B162" s="152"/>
       <c r="C162" s="168" t="s">
         <v>245</v>
@@ -20232,7 +20304,7 @@
         <v>vendor7</v>
       </c>
     </row>
-    <row r="163" spans="2:19">
+    <row r="163" spans="2:19" ht="26">
       <c r="B163" s="152"/>
       <c r="C163" s="168" t="s">
         <v>235</v>
@@ -20363,7 +20435,7 @@
         <v>vendor7</v>
       </c>
     </row>
-    <row r="166" spans="2:19">
+    <row r="166" spans="2:19" ht="26">
       <c r="B166" s="150">
         <v>39</v>
       </c>
@@ -20410,7 +20482,7 @@
         <v>vendor7</v>
       </c>
     </row>
-    <row r="167" spans="2:19">
+    <row r="167" spans="2:19" ht="26">
       <c r="B167" s="152"/>
       <c r="C167" s="168" t="s">
         <v>245</v>
@@ -20455,7 +20527,7 @@
         <v>vendor7</v>
       </c>
     </row>
-    <row r="168" spans="2:19">
+    <row r="168" spans="2:19" ht="26">
       <c r="B168" s="152"/>
       <c r="C168" s="168" t="s">
         <v>235</v>
@@ -20586,7 +20658,7 @@
         <v>vendor7</v>
       </c>
     </row>
-    <row r="171" spans="2:19">
+    <row r="171" spans="2:19" ht="26">
       <c r="B171" s="150">
         <v>40</v>
       </c>
@@ -20633,7 +20705,7 @@
         <v>vendor8</v>
       </c>
     </row>
-    <row r="172" spans="2:19">
+    <row r="172" spans="2:19" ht="26">
       <c r="B172" s="152"/>
       <c r="C172" s="168" t="s">
         <v>245</v>
@@ -20678,7 +20750,7 @@
         <v>vendor8</v>
       </c>
     </row>
-    <row r="173" spans="2:19">
+    <row r="173" spans="2:19" ht="26">
       <c r="B173" s="152"/>
       <c r="C173" s="168" t="s">
         <v>235</v>
@@ -20816,7 +20888,7 @@
       <c r="B176" s="144">
         <v>41</v>
       </c>
-      <c r="C176" s="371" t="s">
+      <c r="C176" s="356" t="s">
         <v>250</v>
       </c>
       <c r="D176" s="169" t="s">
@@ -20856,8 +20928,8 @@
       </c>
     </row>
     <row r="177" spans="1:18">
-      <c r="B177" s="373"/>
-      <c r="C177" s="372"/>
+      <c r="B177" s="347"/>
+      <c r="C177" s="339"/>
       <c r="D177" s="170" t="s">
         <v>87</v>
       </c>
@@ -20895,8 +20967,8 @@
       </c>
     </row>
     <row r="178" spans="1:18">
-      <c r="B178" s="373"/>
-      <c r="C178" s="372"/>
+      <c r="B178" s="347"/>
+      <c r="C178" s="339"/>
       <c r="D178" s="171" t="s">
         <v>244</v>
       </c>
@@ -20936,8 +21008,8 @@
       </c>
     </row>
     <row r="179" spans="1:18">
-      <c r="B179" s="373"/>
-      <c r="C179" s="372"/>
+      <c r="B179" s="347"/>
+      <c r="C179" s="339"/>
       <c r="D179" s="171" t="s">
         <v>252</v>
       </c>
@@ -20975,8 +21047,8 @@
       </c>
     </row>
     <row r="180" spans="1:18">
-      <c r="B180" s="373"/>
-      <c r="C180" s="372"/>
+      <c r="B180" s="347"/>
+      <c r="C180" s="339"/>
       <c r="D180" s="172" t="s">
         <v>253</v>
       </c>
@@ -21013,9 +21085,9 @@
         <v>vendor2</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
-      <c r="B181" s="373"/>
-      <c r="C181" s="372"/>
+    <row r="181" spans="1:18" ht="26">
+      <c r="B181" s="347"/>
+      <c r="C181" s="339"/>
       <c r="D181" s="173" t="s">
         <v>254</v>
       </c>
@@ -21053,8 +21125,8 @@
       </c>
     </row>
     <row r="182" spans="1:18">
-      <c r="B182" s="373"/>
-      <c r="C182" s="372"/>
+      <c r="B182" s="347"/>
+      <c r="C182" s="339"/>
       <c r="D182" s="171" t="s">
         <v>255</v>
       </c>
@@ -21093,9 +21165,9 @@
         <v>vendor2</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="32.1" customHeight="1">
-      <c r="B183" s="373"/>
-      <c r="C183" s="372"/>
+    <row r="183" spans="1:18" ht="32" customHeight="1">
+      <c r="B183" s="347"/>
+      <c r="C183" s="339"/>
       <c r="D183" s="142" t="s">
         <v>256</v>
       </c>
@@ -21137,7 +21209,7 @@
       <c r="B184" s="144">
         <v>42</v>
       </c>
-      <c r="C184" s="372" t="s">
+      <c r="C184" s="339" t="s">
         <v>257</v>
       </c>
       <c r="D184" s="169" t="s">
@@ -21178,8 +21250,8 @@
     </row>
     <row r="185" spans="1:18" s="174" customFormat="1">
       <c r="A185" s="137"/>
-      <c r="B185" s="373"/>
-      <c r="C185" s="372"/>
+      <c r="B185" s="347"/>
+      <c r="C185" s="339"/>
       <c r="D185" s="170" t="s">
         <v>191</v>
       </c>
@@ -21217,8 +21289,8 @@
       </c>
     </row>
     <row r="186" spans="1:18">
-      <c r="B186" s="373"/>
-      <c r="C186" s="372"/>
+      <c r="B186" s="347"/>
+      <c r="C186" s="339"/>
       <c r="D186" s="171" t="s">
         <v>89</v>
       </c>
@@ -21256,8 +21328,8 @@
       </c>
     </row>
     <row r="187" spans="1:18">
-      <c r="B187" s="373"/>
-      <c r="C187" s="372"/>
+      <c r="B187" s="347"/>
+      <c r="C187" s="339"/>
       <c r="D187" s="171" t="s">
         <v>91</v>
       </c>
@@ -21295,8 +21367,8 @@
       </c>
     </row>
     <row r="188" spans="1:18">
-      <c r="B188" s="373"/>
-      <c r="C188" s="372"/>
+      <c r="B188" s="347"/>
+      <c r="C188" s="339"/>
       <c r="D188" s="172" t="s">
         <v>258</v>
       </c>
@@ -21333,9 +21405,9 @@
         <v>vendor2</v>
       </c>
     </row>
-    <row r="189" spans="1:18">
-      <c r="B189" s="373"/>
-      <c r="C189" s="372"/>
+    <row r="189" spans="1:18" ht="26">
+      <c r="B189" s="347"/>
+      <c r="C189" s="339"/>
       <c r="D189" s="173" t="s">
         <v>259</v>
       </c>
@@ -21373,8 +21445,8 @@
       </c>
     </row>
     <row r="190" spans="1:18">
-      <c r="B190" s="373"/>
-      <c r="C190" s="372"/>
+      <c r="B190" s="347"/>
+      <c r="C190" s="339"/>
       <c r="D190" s="171" t="s">
         <v>255</v>
       </c>
@@ -21412,8 +21484,8 @@
       </c>
     </row>
     <row r="191" spans="1:18" ht="34.5" customHeight="1">
-      <c r="B191" s="375"/>
-      <c r="C191" s="374"/>
+      <c r="B191" s="358"/>
+      <c r="C191" s="357"/>
       <c r="D191" s="142" t="s">
         <v>256</v>
       </c>
@@ -21452,10 +21524,10 @@
     </row>
     <row r="192" spans="1:18" s="174" customFormat="1">
       <c r="A192" s="137"/>
-      <c r="B192" s="368">
+      <c r="B192" s="346">
         <v>43</v>
       </c>
-      <c r="C192" s="331" t="s">
+      <c r="C192" s="352" t="s">
         <v>260</v>
       </c>
       <c r="D192" s="169" t="s">
@@ -21496,8 +21568,8 @@
     </row>
     <row r="193" spans="1:18" s="174" customFormat="1">
       <c r="A193" s="137"/>
-      <c r="B193" s="373"/>
-      <c r="C193" s="311"/>
+      <c r="B193" s="347"/>
+      <c r="C193" s="353"/>
       <c r="D193" s="170" t="s">
         <v>191</v>
       </c>
@@ -21535,8 +21607,8 @@
       </c>
     </row>
     <row r="194" spans="1:18">
-      <c r="B194" s="373"/>
-      <c r="C194" s="311"/>
+      <c r="B194" s="347"/>
+      <c r="C194" s="353"/>
       <c r="D194" s="171" t="s">
         <v>89</v>
       </c>
@@ -21574,8 +21646,8 @@
       </c>
     </row>
     <row r="195" spans="1:18">
-      <c r="B195" s="373"/>
-      <c r="C195" s="311"/>
+      <c r="B195" s="347"/>
+      <c r="C195" s="353"/>
       <c r="D195" s="171" t="s">
         <v>91</v>
       </c>
@@ -21613,8 +21685,8 @@
       </c>
     </row>
     <row r="196" spans="1:18">
-      <c r="B196" s="373"/>
-      <c r="C196" s="311"/>
+      <c r="B196" s="347"/>
+      <c r="C196" s="353"/>
       <c r="D196" s="172" t="s">
         <v>253</v>
       </c>
@@ -21652,8 +21724,8 @@
       </c>
     </row>
     <row r="197" spans="1:18">
-      <c r="B197" s="373"/>
-      <c r="C197" s="311"/>
+      <c r="B197" s="347"/>
+      <c r="C197" s="353"/>
       <c r="D197" s="172" t="s">
         <v>99</v>
       </c>
@@ -21691,8 +21763,8 @@
       </c>
     </row>
     <row r="198" spans="1:18">
-      <c r="B198" s="373"/>
-      <c r="C198" s="311"/>
+      <c r="B198" s="347"/>
+      <c r="C198" s="353"/>
       <c r="D198" s="171" t="s">
         <v>255</v>
       </c>
@@ -21731,8 +21803,8 @@
         <v>vendor2</v>
       </c>
     </row>
-    <row r="199" spans="1:18">
-      <c r="B199" s="375"/>
+    <row r="199" spans="1:18" ht="26">
+      <c r="B199" s="358"/>
       <c r="C199" s="161"/>
       <c r="D199" s="142" t="s">
         <v>261</v>
@@ -38452,18 +38524,29 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C192:C198"/>
+    <mergeCell ref="B154:B160"/>
+    <mergeCell ref="C154:C160"/>
+    <mergeCell ref="C176:C183"/>
+    <mergeCell ref="B177:B183"/>
+    <mergeCell ref="C184:C191"/>
+    <mergeCell ref="B185:B191"/>
+    <mergeCell ref="B192:B199"/>
+    <mergeCell ref="C131:C134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="B140:B146"/>
+    <mergeCell ref="C140:C146"/>
+    <mergeCell ref="B147:B153"/>
+    <mergeCell ref="C147:C153"/>
+    <mergeCell ref="C127:C130"/>
+    <mergeCell ref="C93:C97"/>
+    <mergeCell ref="C99:C103"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C68"/>
+    <mergeCell ref="C69:C73"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="C75:C80"/>
     <mergeCell ref="C105:C109"/>
     <mergeCell ref="C57:C61"/>
     <mergeCell ref="C19:C20"/>
@@ -38480,29 +38563,18 @@
     <mergeCell ref="C81:C85"/>
     <mergeCell ref="B87:B89"/>
     <mergeCell ref="C87:C92"/>
-    <mergeCell ref="C93:C97"/>
-    <mergeCell ref="C99:C103"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="C63:C68"/>
-    <mergeCell ref="C69:C73"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="C75:C80"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="C192:C198"/>
-    <mergeCell ref="B154:B160"/>
-    <mergeCell ref="C154:C160"/>
-    <mergeCell ref="C176:C183"/>
-    <mergeCell ref="B177:B183"/>
-    <mergeCell ref="C184:C191"/>
-    <mergeCell ref="B185:B191"/>
-    <mergeCell ref="B192:B199"/>
-    <mergeCell ref="C131:C134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="B140:B146"/>
-    <mergeCell ref="C140:C146"/>
-    <mergeCell ref="B147:B153"/>
-    <mergeCell ref="C147:C153"/>
-    <mergeCell ref="C127:C130"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -38514,7 +38586,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D0F5A9-F01B-4774-AF00-FFB99B561984}">
   <dimension ref="A2:B3"/>
-  <sheetFormatPr defaultRowHeight="12.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
@@ -38543,33 +38615,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y181"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="35.450000000000003"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" style="178" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="101.5703125" style="137" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" style="180" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="137" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="137" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="137" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="137" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="137" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="137" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="137" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="137" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.85546875" style="137" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="178" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="101.5" style="137" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="180" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="137" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="137" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" style="137" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" style="137" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" style="137" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31.5703125" style="180" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.42578125" style="137" customWidth="1"/>
-    <col min="20" max="20" width="51.28515625" style="137" customWidth="1"/>
-    <col min="21" max="21" width="43.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="9.140625" style="137"/>
-    <col min="24" max="24" width="3.5703125" style="137" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="88.28515625" style="137" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="137"/>
+    <col min="16" max="16" width="18.1640625" style="137" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.5" style="180" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.5" style="137" customWidth="1"/>
+    <col min="20" max="20" width="51.33203125" style="137" customWidth="1"/>
+    <col min="21" max="21" width="43.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="9.1640625" style="137"/>
+    <col min="24" max="24" width="3.5" style="137" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="88.33203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.1640625" style="137"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -38727,11 +38799,11 @@
       </c>
     </row>
     <row r="4" spans="1:20" s="299" customFormat="1" ht="40.5" customHeight="1">
-      <c r="B4" s="304" t="s">
+      <c r="B4" s="366" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="304"/>
-      <c r="D4" s="304"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
       <c r="E4" s="300"/>
       <c r="H4" s="300"/>
       <c r="Q4" s="301"/>
@@ -38740,7 +38812,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="139" customFormat="1" ht="107.45">
+    <row r="5" spans="1:20" s="139" customFormat="1" ht="110">
       <c r="A5" s="175" t="s">
         <v>171</v>
       </c>
@@ -38802,8 +38874,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="312">
+    <row r="6" spans="1:20" ht="26">
+      <c r="A6" s="373">
         <v>44</v>
       </c>
       <c r="B6" s="184" t="s">
@@ -38849,7 +38921,7 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="312"/>
+      <c r="A7" s="373"/>
       <c r="B7" s="185" t="s">
         <v>272</v>
       </c>
@@ -38893,7 +38965,7 @@
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="312"/>
+      <c r="A8" s="373"/>
       <c r="B8" s="185" t="s">
         <v>273</v>
       </c>
@@ -38937,7 +39009,7 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="312"/>
+      <c r="A9" s="373"/>
       <c r="B9" s="185"/>
       <c r="C9" s="187" t="s">
         <v>91</v>
@@ -38979,7 +39051,7 @@
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="312"/>
+      <c r="A10" s="373"/>
       <c r="B10" s="185"/>
       <c r="C10" s="187" t="s">
         <v>258</v>
@@ -39023,7 +39095,7 @@
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="312"/>
+      <c r="A11" s="373"/>
       <c r="B11" s="185"/>
       <c r="C11" s="149" t="s">
         <v>99</v>
@@ -39065,7 +39137,7 @@
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="312"/>
+      <c r="A12" s="373"/>
       <c r="B12" s="185"/>
       <c r="C12" s="149" t="s">
         <v>255</v>
@@ -39107,7 +39179,7 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="313"/>
+      <c r="A13" s="374"/>
       <c r="B13" s="185"/>
       <c r="C13" s="187" t="s">
         <v>261</v>
@@ -39149,7 +39221,7 @@
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="314">
+      <c r="A14" s="375">
         <v>45</v>
       </c>
       <c r="B14" s="157" t="s">
@@ -39194,8 +39266,8 @@
         <v>vendor 14</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="315"/>
+    <row r="15" spans="1:20" ht="26">
+      <c r="A15" s="376"/>
       <c r="B15" s="184" t="s">
         <v>275</v>
       </c>
@@ -39241,7 +39313,7 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="315"/>
+      <c r="A16" s="376"/>
       <c r="B16" s="185" t="s">
         <v>276</v>
       </c>
@@ -39285,7 +39357,7 @@
       </c>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="316"/>
+      <c r="A17" s="377"/>
       <c r="B17" s="185"/>
       <c r="C17" s="278">
         <v>20000</v>
@@ -39327,7 +39399,7 @@
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="317">
+      <c r="A18" s="378">
         <v>46</v>
       </c>
       <c r="B18" s="295" t="s">
@@ -39375,7 +39447,7 @@
       </c>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="318"/>
+      <c r="A19" s="379"/>
       <c r="B19" s="296" t="s">
         <v>279</v>
       </c>
@@ -39421,7 +39493,7 @@
       </c>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="318"/>
+      <c r="A20" s="379"/>
       <c r="B20" s="296" t="s">
         <v>280</v>
       </c>
@@ -39467,7 +39539,7 @@
       </c>
     </row>
     <row r="21" spans="1:20">
-      <c r="A21" s="318"/>
+      <c r="A21" s="379"/>
       <c r="B21" s="296" t="s">
         <v>281</v>
       </c>
@@ -39515,7 +39587,7 @@
       </c>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="319"/>
+      <c r="A22" s="380"/>
       <c r="B22" s="289"/>
       <c r="C22" s="287" t="s">
         <v>282</v>
@@ -39559,7 +39631,7 @@
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="320">
+      <c r="A23" s="381">
         <v>47</v>
       </c>
       <c r="B23" s="161" t="s">
@@ -39612,7 +39684,7 @@
       </c>
     </row>
     <row r="24" spans="1:20">
-      <c r="A24" s="312"/>
+      <c r="A24" s="373"/>
       <c r="B24" s="138" t="s">
         <v>284</v>
       </c>
@@ -39663,7 +39735,7 @@
       </c>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="313"/>
+      <c r="A25" s="374"/>
       <c r="B25" s="138" t="s">
         <v>285</v>
       </c>
@@ -39710,7 +39782,7 @@
       </c>
     </row>
     <row r="26" spans="1:20">
-      <c r="A26" s="320">
+      <c r="A26" s="381">
         <v>48</v>
       </c>
       <c r="B26" s="138" t="s">
@@ -39763,7 +39835,7 @@
       </c>
     </row>
     <row r="27" spans="1:20">
-      <c r="A27" s="312"/>
+      <c r="A27" s="373"/>
       <c r="B27" s="138" t="s">
         <v>287</v>
       </c>
@@ -39814,7 +39886,7 @@
       </c>
     </row>
     <row r="28" spans="1:20">
-      <c r="A28" s="312"/>
+      <c r="A28" s="373"/>
       <c r="B28" s="157" t="s">
         <v>288</v>
       </c>
@@ -40267,7 +40339,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="38" spans="1:22" s="174" customFormat="1" ht="71.099999999999994">
+    <row r="38" spans="1:22" s="174" customFormat="1" ht="52">
       <c r="A38" s="195">
         <v>51</v>
       </c>
@@ -40315,7 +40387,7 @@
       <c r="U38" s="137"/>
       <c r="V38" s="137"/>
     </row>
-    <row r="39" spans="1:22" s="174" customFormat="1">
+    <row r="39" spans="1:22" s="174" customFormat="1" ht="26">
       <c r="A39" s="197"/>
       <c r="B39" s="160" t="s">
         <v>300</v>
@@ -40361,7 +40433,7 @@
       <c r="U39" s="137"/>
       <c r="V39" s="137"/>
     </row>
-    <row r="40" spans="1:22" s="174" customFormat="1">
+    <row r="40" spans="1:22" s="174" customFormat="1" ht="26">
       <c r="A40" s="197"/>
       <c r="B40" s="160" t="s">
         <v>302</v>
@@ -40407,7 +40479,7 @@
       <c r="U40" s="137"/>
       <c r="V40" s="137"/>
     </row>
-    <row r="41" spans="1:22" s="174" customFormat="1" ht="41.1" customHeight="1">
+    <row r="41" spans="1:22" s="174" customFormat="1" ht="41" customHeight="1">
       <c r="A41" s="198">
         <v>52</v>
       </c>
@@ -40479,7 +40551,7 @@
       <c r="U42" s="137"/>
       <c r="V42" s="137"/>
     </row>
-    <row r="43" spans="1:22" s="174" customFormat="1">
+    <row r="43" spans="1:22" s="174" customFormat="1" ht="26">
       <c r="A43" s="200"/>
       <c r="B43" s="201" t="s">
         <v>307</v>
@@ -40525,7 +40597,7 @@
       <c r="U43" s="137"/>
       <c r="V43" s="137"/>
     </row>
-    <row r="44" spans="1:22" s="174" customFormat="1">
+    <row r="44" spans="1:22" s="174" customFormat="1" ht="26">
       <c r="A44" s="200"/>
       <c r="B44" s="201" t="s">
         <v>309</v>
@@ -40571,7 +40643,7 @@
       <c r="U44" s="137"/>
       <c r="V44" s="137"/>
     </row>
-    <row r="45" spans="1:22" s="174" customFormat="1" ht="106.5">
+    <row r="45" spans="1:22" s="174" customFormat="1" ht="78">
       <c r="A45" s="198">
         <v>53</v>
       </c>
@@ -40619,7 +40691,7 @@
       <c r="U45" s="137"/>
       <c r="V45" s="137"/>
     </row>
-    <row r="46" spans="1:22" s="174" customFormat="1">
+    <row r="46" spans="1:22" s="174" customFormat="1" ht="26">
       <c r="A46" s="200"/>
       <c r="B46" s="164" t="s">
         <v>307</v>
@@ -40664,7 +40736,7 @@
       </c>
       <c r="U46" s="137"/>
     </row>
-    <row r="47" spans="1:22" s="174" customFormat="1">
+    <row r="47" spans="1:22" s="174" customFormat="1" ht="26">
       <c r="A47" s="200"/>
       <c r="B47" s="164" t="s">
         <v>313</v>
@@ -40709,7 +40781,7 @@
       </c>
       <c r="U47" s="137"/>
     </row>
-    <row r="48" spans="1:22" s="174" customFormat="1" ht="106.5">
+    <row r="48" spans="1:22" s="174" customFormat="1" ht="78">
       <c r="A48" s="198">
         <v>54</v>
       </c>
@@ -40756,7 +40828,7 @@
       </c>
       <c r="U48" s="137"/>
     </row>
-    <row r="49" spans="1:21" s="174" customFormat="1">
+    <row r="49" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A49" s="200"/>
       <c r="B49" s="164" t="s">
         <v>307</v>
@@ -40801,7 +40873,7 @@
       </c>
       <c r="U49" s="137"/>
     </row>
-    <row r="50" spans="1:21" s="174" customFormat="1">
+    <row r="50" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A50" s="200"/>
       <c r="B50" s="164" t="s">
         <v>315</v>
@@ -40846,7 +40918,7 @@
       </c>
       <c r="U50" s="137"/>
     </row>
-    <row r="51" spans="1:21" s="174" customFormat="1" ht="106.5">
+    <row r="51" spans="1:21" s="174" customFormat="1" ht="78">
       <c r="A51" s="195">
         <v>55</v>
       </c>
@@ -40891,7 +40963,7 @@
       </c>
       <c r="U51" s="137"/>
     </row>
-    <row r="52" spans="1:21" s="174" customFormat="1">
+    <row r="52" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A52" s="197"/>
       <c r="B52" s="164" t="s">
         <v>317</v>
@@ -40934,7 +41006,7 @@
       </c>
       <c r="U52" s="137"/>
     </row>
-    <row r="53" spans="1:21" s="174" customFormat="1">
+    <row r="53" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A53" s="197"/>
       <c r="B53" s="164" t="s">
         <v>318</v>
@@ -40977,7 +41049,7 @@
       </c>
       <c r="U53" s="137"/>
     </row>
-    <row r="54" spans="1:21" s="174" customFormat="1" ht="177.6">
+    <row r="54" spans="1:21" s="174" customFormat="1" ht="130">
       <c r="A54" s="195">
         <v>56</v>
       </c>
@@ -41022,7 +41094,7 @@
       </c>
       <c r="U54" s="137"/>
     </row>
-    <row r="55" spans="1:21" s="174" customFormat="1">
+    <row r="55" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A55" s="197"/>
       <c r="B55" s="164" t="s">
         <v>307</v>
@@ -41065,7 +41137,7 @@
       </c>
       <c r="U55" s="137"/>
     </row>
-    <row r="56" spans="1:21" s="174" customFormat="1">
+    <row r="56" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A56" s="197"/>
       <c r="B56" s="164" t="s">
         <v>309</v>
@@ -41108,7 +41180,7 @@
       </c>
       <c r="U56" s="137"/>
     </row>
-    <row r="57" spans="1:21" s="174" customFormat="1" ht="141.94999999999999">
+    <row r="57" spans="1:21" s="174" customFormat="1" ht="104">
       <c r="A57" s="198">
         <v>57</v>
       </c>
@@ -41153,7 +41225,7 @@
       </c>
       <c r="U57" s="137"/>
     </row>
-    <row r="58" spans="1:21" s="174" customFormat="1">
+    <row r="58" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A58" s="200"/>
       <c r="B58" s="164" t="s">
         <v>321</v>
@@ -41196,7 +41268,7 @@
       </c>
       <c r="U58" s="137"/>
     </row>
-    <row r="59" spans="1:21" s="174" customFormat="1">
+    <row r="59" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A59" s="200"/>
       <c r="B59" s="164" t="s">
         <v>307</v>
@@ -41239,7 +41311,7 @@
       </c>
       <c r="U59" s="137"/>
     </row>
-    <row r="60" spans="1:21" s="174" customFormat="1" ht="177.6">
+    <row r="60" spans="1:21" s="174" customFormat="1" ht="130">
       <c r="A60" s="198">
         <v>58</v>
       </c>
@@ -41284,7 +41356,7 @@
       </c>
       <c r="U60" s="137"/>
     </row>
-    <row r="61" spans="1:21" s="174" customFormat="1">
+    <row r="61" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A61" s="200"/>
       <c r="B61" s="201" t="s">
         <v>323</v>
@@ -41327,7 +41399,7 @@
       </c>
       <c r="U61" s="137"/>
     </row>
-    <row r="62" spans="1:21" s="174" customFormat="1">
+    <row r="62" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A62" s="200"/>
       <c r="B62" s="202" t="s">
         <v>307</v>
@@ -41370,7 +41442,7 @@
       </c>
       <c r="U62" s="137"/>
     </row>
-    <row r="63" spans="1:21" s="174" customFormat="1">
+    <row r="63" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A63" s="200"/>
       <c r="B63" s="203" t="s">
         <v>324</v>
@@ -41402,12 +41474,12 @@
       </c>
       <c r="R63" s="187"/>
       <c r="S63" s="88"/>
-      <c r="T63" s="305" t="s">
+      <c r="T63" s="367" t="s">
         <v>326</v>
       </c>
       <c r="U63" s="137"/>
     </row>
-    <row r="64" spans="1:21" s="174" customFormat="1" ht="106.5">
+    <row r="64" spans="1:21" s="174" customFormat="1" ht="52">
       <c r="A64" s="204"/>
       <c r="B64" s="205" t="s">
         <v>327</v>
@@ -41439,7 +41511,7 @@
       </c>
       <c r="R64" s="187"/>
       <c r="S64" s="88"/>
-      <c r="T64" s="306"/>
+      <c r="T64" s="368"/>
       <c r="U64" s="137"/>
     </row>
     <row r="65" spans="1:21" s="174" customFormat="1">
@@ -41479,7 +41551,7 @@
       </c>
       <c r="U65" s="137"/>
     </row>
-    <row r="66" spans="1:21" s="174" customFormat="1" ht="71.099999999999994">
+    <row r="66" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A66" s="207">
         <v>59</v>
       </c>
@@ -41600,7 +41672,7 @@
       </c>
       <c r="U68" s="137"/>
     </row>
-    <row r="69" spans="1:21" s="174" customFormat="1">
+    <row r="69" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A69" s="120">
         <v>60</v>
       </c>
@@ -41675,10 +41747,10 @@
       <c r="U70" s="137"/>
     </row>
     <row r="71" spans="1:21" s="174" customFormat="1">
-      <c r="A71" s="310">
+      <c r="A71" s="372">
         <v>61</v>
       </c>
-      <c r="B71" s="322" t="s">
+      <c r="B71" s="360" t="s">
         <v>341</v>
       </c>
       <c r="C71" s="277" t="s">
@@ -41722,8 +41794,8 @@
       <c r="U71" s="137"/>
     </row>
     <row r="72" spans="1:21">
-      <c r="A72" s="310"/>
-      <c r="B72" s="322"/>
+      <c r="A72" s="372"/>
+      <c r="B72" s="360"/>
       <c r="C72" s="187" t="s">
         <v>343</v>
       </c>
@@ -41764,8 +41836,8 @@
       </c>
     </row>
     <row r="73" spans="1:21">
-      <c r="A73" s="310"/>
-      <c r="B73" s="322"/>
+      <c r="A73" s="372"/>
+      <c r="B73" s="360"/>
       <c r="C73" s="187" t="s">
         <v>345</v>
       </c>
@@ -41806,8 +41878,8 @@
       </c>
     </row>
     <row r="74" spans="1:21">
-      <c r="A74" s="310"/>
-      <c r="B74" s="322"/>
+      <c r="A74" s="372"/>
+      <c r="B74" s="360"/>
       <c r="C74" s="187" t="s">
         <v>347</v>
       </c>
@@ -41848,8 +41920,8 @@
       </c>
     </row>
     <row r="75" spans="1:21">
-      <c r="A75" s="321"/>
-      <c r="B75" s="323"/>
+      <c r="A75" s="382"/>
+      <c r="B75" s="361"/>
       <c r="C75" s="187" t="s">
         <v>349</v>
       </c>
@@ -41890,10 +41962,10 @@
       </c>
     </row>
     <row r="76" spans="1:21" s="174" customFormat="1">
-      <c r="A76" s="324">
+      <c r="A76" s="335">
         <v>62</v>
       </c>
-      <c r="B76" s="323" t="s">
+      <c r="B76" s="361" t="s">
         <v>351</v>
       </c>
       <c r="C76" s="187" t="s">
@@ -41937,8 +42009,8 @@
       <c r="U76" s="137"/>
     </row>
     <row r="77" spans="1:21" s="174" customFormat="1">
-      <c r="A77" s="325"/>
-      <c r="B77" s="326"/>
+      <c r="A77" s="362"/>
+      <c r="B77" s="383"/>
       <c r="C77" s="187" t="s">
         <v>354</v>
       </c>
@@ -41980,8 +42052,8 @@
       <c r="U77" s="137"/>
     </row>
     <row r="78" spans="1:21" s="174" customFormat="1">
-      <c r="A78" s="325"/>
-      <c r="B78" s="326"/>
+      <c r="A78" s="362"/>
+      <c r="B78" s="383"/>
       <c r="C78" s="187" t="s">
         <v>356</v>
       </c>
@@ -42023,8 +42095,8 @@
       <c r="U78" s="137"/>
     </row>
     <row r="79" spans="1:21">
-      <c r="A79" s="325"/>
-      <c r="B79" s="326"/>
+      <c r="A79" s="362"/>
+      <c r="B79" s="383"/>
       <c r="C79" s="187" t="s">
         <v>358</v>
       </c>
@@ -42065,8 +42137,8 @@
       </c>
     </row>
     <row r="80" spans="1:21">
-      <c r="A80" s="325"/>
-      <c r="B80" s="326"/>
+      <c r="A80" s="362"/>
+      <c r="B80" s="383"/>
       <c r="C80" s="187" t="s">
         <v>332</v>
       </c>
@@ -42106,7 +42178,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="39.6" customHeight="1">
+    <row r="81" spans="1:20" ht="39.5" customHeight="1">
       <c r="A81" s="113">
         <v>63</v>
       </c>
@@ -42152,7 +42224,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="41.1" customHeight="1">
+    <row r="82" spans="1:20" ht="41" customHeight="1">
       <c r="A82" s="113">
         <v>64</v>
       </c>
@@ -42198,7 +42270,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="83" spans="1:20">
+    <row r="83" spans="1:20" ht="26">
       <c r="A83" s="113">
         <v>65</v>
       </c>
@@ -42244,7 +42316,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="84" spans="1:20">
+    <row r="84" spans="1:20" ht="26">
       <c r="A84" s="113">
         <v>66</v>
       </c>
@@ -42290,7 +42362,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="39.6" customHeight="1">
+    <row r="85" spans="1:20" ht="39.5" customHeight="1">
       <c r="A85" s="113">
         <v>67</v>
       </c>
@@ -42378,7 +42450,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="87" spans="1:20">
+    <row r="87" spans="1:20" ht="26">
       <c r="A87" s="113">
         <v>69</v>
       </c>
@@ -42422,7 +42494,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="88" spans="1:20">
+    <row r="88" spans="1:20" ht="26">
       <c r="A88" s="113">
         <v>70</v>
       </c>
@@ -42512,7 +42584,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="41.1" customHeight="1">
+    <row r="90" spans="1:20" ht="41" customHeight="1">
       <c r="A90" s="113">
         <v>72</v>
       </c>
@@ -42558,7 +42630,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="91" spans="1:20">
+    <row r="91" spans="1:20" ht="26">
       <c r="A91" s="113">
         <v>73</v>
       </c>
@@ -42604,7 +42676,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="92" spans="1:20">
+    <row r="92" spans="1:20" ht="26">
       <c r="A92" s="113">
         <v>74</v>
       </c>
@@ -43421,7 +43493,7 @@
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="T109" s="307" t="s">
+      <c r="T109" s="369" t="s">
         <v>390</v>
       </c>
     </row>
@@ -43462,7 +43534,7 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="T110" s="308"/>
+      <c r="T110" s="370"/>
     </row>
     <row r="111" spans="1:20">
       <c r="A111" s="113"/>
@@ -43501,13 +43573,13 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="T111" s="309"/>
+      <c r="T111" s="371"/>
     </row>
     <row r="112" spans="1:20" s="174" customFormat="1">
-      <c r="A112" s="325">
+      <c r="A112" s="362">
         <v>91</v>
       </c>
-      <c r="B112" s="326" t="s">
+      <c r="B112" s="383" t="s">
         <v>393</v>
       </c>
       <c r="C112" s="187" t="s">
@@ -43552,8 +43624,8 @@
       </c>
     </row>
     <row r="113" spans="1:25">
-      <c r="A113" s="327"/>
-      <c r="B113" s="328"/>
+      <c r="A113" s="331"/>
+      <c r="B113" s="384"/>
       <c r="C113" s="187" t="s">
         <v>332</v>
       </c>
@@ -43597,7 +43669,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" ht="26">
       <c r="A114" s="214">
         <v>92</v>
       </c>
@@ -43654,8 +43726,8 @@
       </c>
     </row>
     <row r="115" spans="1:25">
-      <c r="A115" s="310"/>
-      <c r="B115" s="311" t="s">
+      <c r="A115" s="372"/>
+      <c r="B115" s="353" t="s">
         <v>399</v>
       </c>
       <c r="C115" s="187" t="s">
@@ -43702,8 +43774,8 @@
       </c>
     </row>
     <row r="116" spans="1:25">
-      <c r="A116" s="310"/>
-      <c r="B116" s="311"/>
+      <c r="A116" s="372"/>
+      <c r="B116" s="353"/>
       <c r="C116" s="187" t="s">
         <v>332</v>
       </c>
@@ -43748,8 +43820,8 @@
       </c>
     </row>
     <row r="117" spans="1:25">
-      <c r="A117" s="310"/>
-      <c r="B117" s="311"/>
+      <c r="A117" s="372"/>
+      <c r="B117" s="353"/>
       <c r="C117" s="187" t="s">
         <v>401</v>
       </c>
@@ -43839,7 +43911,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" ht="26">
       <c r="A119" s="214">
         <v>93</v>
       </c>
@@ -43889,7 +43961,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" ht="26">
       <c r="A120" s="210"/>
       <c r="B120" s="164" t="s">
         <v>399</v>
@@ -44075,7 +44147,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" ht="26">
       <c r="A124" s="214">
         <v>94</v>
       </c>
@@ -44125,7 +44197,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" ht="26">
       <c r="A125" s="210"/>
       <c r="B125" s="216" t="s">
         <v>399</v>
@@ -44312,10 +44384,10 @@
       </c>
     </row>
     <row r="129" spans="1:20">
-      <c r="A129" s="325">
+      <c r="A129" s="362">
         <v>95</v>
       </c>
-      <c r="B129" s="329" t="s">
+      <c r="B129" s="363" t="s">
         <v>405</v>
       </c>
       <c r="C129" s="187" t="s">
@@ -44360,8 +44432,8 @@
       </c>
     </row>
     <row r="130" spans="1:20">
-      <c r="A130" s="325"/>
-      <c r="B130" s="329"/>
+      <c r="A130" s="362"/>
+      <c r="B130" s="363"/>
       <c r="C130" s="187" t="s">
         <v>407</v>
       </c>
@@ -44404,10 +44476,10 @@
       </c>
     </row>
     <row r="131" spans="1:20">
-      <c r="A131" s="330">
+      <c r="A131" s="364">
         <v>96</v>
       </c>
-      <c r="B131" s="329" t="s">
+      <c r="B131" s="363" t="s">
         <v>409</v>
       </c>
       <c r="C131" s="277" t="s">
@@ -44450,8 +44522,8 @@
       </c>
     </row>
     <row r="132" spans="1:20">
-      <c r="A132" s="330"/>
-      <c r="B132" s="329"/>
+      <c r="A132" s="364"/>
+      <c r="B132" s="363"/>
       <c r="C132" s="187" t="s">
         <v>410</v>
       </c>
@@ -44492,8 +44564,8 @@
       </c>
     </row>
     <row r="133" spans="1:20">
-      <c r="A133" s="330"/>
-      <c r="B133" s="329"/>
+      <c r="A133" s="364"/>
+      <c r="B133" s="363"/>
       <c r="C133" s="187" t="s">
         <v>412</v>
       </c>
@@ -44534,10 +44606,10 @@
       </c>
     </row>
     <row r="134" spans="1:20">
-      <c r="A134" s="330">
+      <c r="A134" s="364">
         <v>97</v>
       </c>
-      <c r="B134" s="329" t="s">
+      <c r="B134" s="363" t="s">
         <v>413</v>
       </c>
       <c r="C134" s="277" t="s">
@@ -44580,8 +44652,8 @@
       </c>
     </row>
     <row r="135" spans="1:20">
-      <c r="A135" s="330"/>
-      <c r="B135" s="329"/>
+      <c r="A135" s="364"/>
+      <c r="B135" s="363"/>
       <c r="C135" s="187" t="s">
         <v>414</v>
       </c>
@@ -44622,8 +44694,8 @@
       </c>
     </row>
     <row r="136" spans="1:20">
-      <c r="A136" s="330"/>
-      <c r="B136" s="329"/>
+      <c r="A136" s="364"/>
+      <c r="B136" s="363"/>
       <c r="C136" s="187" t="s">
         <v>412</v>
       </c>
@@ -44664,10 +44736,10 @@
       </c>
     </row>
     <row r="137" spans="1:20">
-      <c r="A137" s="330">
+      <c r="A137" s="364">
         <v>98</v>
       </c>
-      <c r="B137" s="329" t="s">
+      <c r="B137" s="363" t="s">
         <v>415</v>
       </c>
       <c r="C137" s="277" t="s">
@@ -44710,8 +44782,8 @@
       </c>
     </row>
     <row r="138" spans="1:20">
-      <c r="A138" s="330"/>
-      <c r="B138" s="329"/>
+      <c r="A138" s="364"/>
+      <c r="B138" s="363"/>
       <c r="C138" s="187" t="s">
         <v>414</v>
       </c>
@@ -44752,8 +44824,8 @@
       </c>
     </row>
     <row r="139" spans="1:20">
-      <c r="A139" s="330"/>
-      <c r="B139" s="329"/>
+      <c r="A139" s="364"/>
+      <c r="B139" s="363"/>
       <c r="C139" s="187" t="s">
         <v>412</v>
       </c>
@@ -44794,10 +44866,10 @@
       </c>
     </row>
     <row r="140" spans="1:20">
-      <c r="A140" s="330">
+      <c r="A140" s="364">
         <v>99</v>
       </c>
-      <c r="B140" s="329" t="s">
+      <c r="B140" s="363" t="s">
         <v>416</v>
       </c>
       <c r="C140" s="277" t="s">
@@ -44840,8 +44912,8 @@
       </c>
     </row>
     <row r="141" spans="1:20">
-      <c r="A141" s="330"/>
-      <c r="B141" s="329"/>
+      <c r="A141" s="364"/>
+      <c r="B141" s="363"/>
       <c r="C141" s="187" t="s">
         <v>414</v>
       </c>
@@ -44882,8 +44954,8 @@
       </c>
     </row>
     <row r="142" spans="1:20">
-      <c r="A142" s="330"/>
-      <c r="B142" s="331"/>
+      <c r="A142" s="364"/>
+      <c r="B142" s="352"/>
       <c r="C142" s="187" t="s">
         <v>412</v>
       </c>
@@ -44923,8 +44995,8 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="143" spans="1:20">
-      <c r="A143" s="330">
+    <row r="143" spans="1:20" ht="26">
+      <c r="A143" s="364">
         <v>100</v>
       </c>
       <c r="B143" s="163" t="s">
@@ -44965,8 +45037,8 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="144" spans="1:20">
-      <c r="A144" s="330"/>
+    <row r="144" spans="1:20" ht="26">
+      <c r="A144" s="364"/>
       <c r="B144" s="164" t="s">
         <v>418</v>
       </c>
@@ -45005,8 +45077,8 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="145" spans="1:20">
-      <c r="A145" s="332"/>
+    <row r="145" spans="1:20" ht="26">
+      <c r="A145" s="365"/>
       <c r="B145" s="164" t="s">
         <v>419</v>
       </c>
@@ -45045,7 +45117,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="146" spans="1:20" s="174" customFormat="1">
+    <row r="146" spans="1:20" s="174" customFormat="1" ht="26">
       <c r="A146" s="198">
         <v>101</v>
       </c>
@@ -45179,7 +45251,7 @@
         <v>vendor 10</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="39.6" customHeight="1">
+    <row r="149" spans="1:20" ht="39.5" customHeight="1">
       <c r="A149" s="195">
         <v>102</v>
       </c>
@@ -45231,7 +45303,7 @@
         <v>vendor 8</v>
       </c>
     </row>
-    <row r="150" spans="1:20">
+    <row r="150" spans="1:20" ht="26">
       <c r="A150" s="197"/>
       <c r="B150" s="218" t="s">
         <v>423</v>
@@ -45281,7 +45353,7 @@
         <v>vendor 8</v>
       </c>
     </row>
-    <row r="151" spans="1:20">
+    <row r="151" spans="1:20" ht="26">
       <c r="A151" s="195">
         <v>103</v>
       </c>
@@ -45335,7 +45407,7 @@
     </row>
     <row r="152" spans="1:20">
       <c r="A152" s="197"/>
-      <c r="B152" s="322" t="s">
+      <c r="B152" s="360" t="s">
         <v>427</v>
       </c>
       <c r="C152" s="279" t="s">
@@ -45383,7 +45455,7 @@
     </row>
     <row r="153" spans="1:20">
       <c r="A153" s="197"/>
-      <c r="B153" s="322"/>
+      <c r="B153" s="360"/>
       <c r="C153" s="279" t="s">
         <v>424</v>
       </c>
@@ -45429,7 +45501,7 @@
     </row>
     <row r="154" spans="1:20">
       <c r="A154" s="220"/>
-      <c r="B154" s="323"/>
+      <c r="B154" s="361"/>
       <c r="C154" s="280" t="s">
         <v>429</v>
       </c>
@@ -45473,7 +45545,7 @@
         <v>vendor 2</v>
       </c>
     </row>
-    <row r="155" spans="1:20" s="174" customFormat="1">
+    <row r="155" spans="1:20" s="174" customFormat="1" ht="26">
       <c r="A155" s="200">
         <v>104</v>
       </c>
@@ -45517,7 +45589,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="156" spans="1:20" s="174" customFormat="1">
+    <row r="156" spans="1:20" s="174" customFormat="1" ht="26">
       <c r="A156" s="195">
         <v>105</v>
       </c>
@@ -45563,7 +45635,7 @@
         <v>vendor 11</v>
       </c>
     </row>
-    <row r="157" spans="1:20" s="174" customFormat="1">
+    <row r="157" spans="1:20" s="174" customFormat="1" ht="26">
       <c r="A157" s="197"/>
       <c r="B157" s="216" t="s">
         <v>433</v>
@@ -45607,7 +45679,7 @@
         <v>vendor 11</v>
       </c>
     </row>
-    <row r="158" spans="1:20">
+    <row r="158" spans="1:20" ht="26">
       <c r="A158" s="197"/>
       <c r="B158" s="216" t="s">
         <v>435</v>
@@ -45693,7 +45765,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="160" spans="1:20">
+    <row r="160" spans="1:20" ht="26">
       <c r="A160" s="198">
         <v>106</v>
       </c>
@@ -45739,7 +45811,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="161" spans="1:21">
+    <row r="161" spans="1:21" ht="26">
       <c r="A161" s="200"/>
       <c r="B161" s="164" t="s">
         <v>439</v>
@@ -45911,7 +45983,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="165" spans="1:21">
+    <row r="165" spans="1:21" ht="26">
       <c r="A165" s="198">
         <v>107</v>
       </c>
@@ -45957,7 +46029,7 @@
         <v>vendor 8</v>
       </c>
     </row>
-    <row r="166" spans="1:21">
+    <row r="166" spans="1:21" ht="26">
       <c r="A166" s="200"/>
       <c r="B166" s="285" t="s">
         <v>442</v>
@@ -46126,7 +46198,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="170" spans="1:21" s="174" customFormat="1">
+    <row r="170" spans="1:21" s="174" customFormat="1" ht="26">
       <c r="A170" s="198">
         <v>108</v>
       </c>
@@ -46265,7 +46337,7 @@
       </c>
       <c r="U172" s="137"/>
     </row>
-    <row r="173" spans="1:21">
+    <row r="173" spans="1:21" ht="26">
       <c r="A173" s="198">
         <v>109</v>
       </c>
@@ -46311,7 +46383,7 @@
         <v>vendor 8</v>
       </c>
     </row>
-    <row r="174" spans="1:21">
+    <row r="174" spans="1:21" ht="26">
       <c r="A174" s="200"/>
       <c r="B174" s="216" t="s">
         <v>446</v>
@@ -46355,7 +46427,7 @@
         <v>vendor 8</v>
       </c>
     </row>
-    <row r="175" spans="1:21">
+    <row r="175" spans="1:21" ht="26">
       <c r="A175" s="200"/>
       <c r="B175" s="216" t="s">
         <v>447</v>
@@ -46399,7 +46471,7 @@
         <v>vendor 9</v>
       </c>
     </row>
-    <row r="176" spans="1:21">
+    <row r="176" spans="1:21" ht="26">
       <c r="A176" s="120"/>
       <c r="B176" s="216" t="s">
         <v>448</v>
@@ -46508,18 +46580,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B152:B154"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="B140:B142"/>
-    <mergeCell ref="A143:A145"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="T63:T64"/>
     <mergeCell ref="T109:T111"/>
@@ -46536,6 +46596,18 @@
     <mergeCell ref="B76:B80"/>
     <mergeCell ref="A112:A113"/>
     <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B152:B154"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="B140:B142"/>
+    <mergeCell ref="A143:A145"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
